--- a/II Library/Localization Strings.xlsx
+++ b/II Library/Localization Strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ibi\Documents\Infirmary Integrated\II Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F61A4F-DAFB-445E-84CB-BF71A767413F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD797020-A86F-4223-8DFE-1F9207FF9771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="203" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45180" yWindow="4680" windowWidth="28800" windowHeight="15410" tabRatio="203" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6160" uniqueCount="5139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6180" uniqueCount="5144">
   <si>
     <t>Temperature</t>
   </si>
@@ -15442,6 +15442,21 @@
   </si>
   <si>
     <t>Infirmary Integrated: Electronic Health Record</t>
+  </si>
+  <si>
+    <t>CHART:Sex</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>CHART:Notes</t>
+  </si>
+  <si>
+    <t>CHART:CodeStatus</t>
+  </si>
+  <si>
+    <t>Code Status</t>
   </si>
 </sst>
 </file>
@@ -15825,22 +15840,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P418"/>
-  <sheetFormatPr defaultColWidth="60.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P421"/>
+  <sheetFormatPr defaultColWidth="60.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="60.7109375" style="2"/>
-    <col min="3" max="4" width="60.7109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="60.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="60.7109375" style="3" customWidth="1"/>
-    <col min="7" max="8" width="60.7109375" style="2" customWidth="1"/>
-    <col min="9" max="10" width="60.7109375" style="3" customWidth="1"/>
-    <col min="11" max="15" width="60.7109375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="60.7109375" style="3"/>
-    <col min="17" max="16384" width="60.7109375" style="2"/>
+    <col min="1" max="1" width="41.1796875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="60.7265625" style="2"/>
+    <col min="3" max="4" width="60.7265625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="60.7265625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="60.7265625" style="3" customWidth="1"/>
+    <col min="7" max="8" width="60.7265625" style="2" customWidth="1"/>
+    <col min="9" max="10" width="60.7265625" style="3" customWidth="1"/>
+    <col min="11" max="15" width="60.7265625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="60.7265625" style="3"/>
+    <col min="17" max="16384" width="60.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -15890,7 +15905,7 @@
         <v>3618</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>3939</v>
       </c>
@@ -15940,7 +15955,7 @@
         <v>3967</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3940</v>
       </c>
@@ -15990,7 +16005,7 @@
         <v>3968</v>
       </c>
     </row>
-    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>41</v>
       </c>
@@ -16040,7 +16055,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>84</v>
       </c>
@@ -16090,7 +16105,7 @@
         <v>2073</v>
       </c>
     </row>
-    <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>85</v>
       </c>
@@ -16140,7 +16155,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>3259</v>
       </c>
@@ -16190,7 +16205,7 @@
         <v>3276</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>4944</v>
       </c>
@@ -16240,8 +16255,8 @@
         <v>4981</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>363</v>
       </c>
@@ -16291,7 +16306,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>331</v>
       </c>
@@ -16341,7 +16356,7 @@
         <v>2080</v>
       </c>
     </row>
-    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>357</v>
       </c>
@@ -16391,7 +16406,7 @@
         <v>4350</v>
       </c>
     </row>
-    <row r="14" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>696</v>
       </c>
@@ -16441,7 +16456,7 @@
         <v>4349</v>
       </c>
     </row>
-    <row r="15" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>1018</v>
       </c>
@@ -16491,7 +16506,7 @@
         <v>4348</v>
       </c>
     </row>
-    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>1200</v>
       </c>
@@ -16541,7 +16556,7 @@
         <v>4347</v>
       </c>
     </row>
-    <row r="17" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>3433</v>
       </c>
@@ -16591,7 +16606,7 @@
         <v>4346</v>
       </c>
     </row>
-    <row r="18" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
         <v>5131</v>
       </c>
@@ -16613,7 +16628,7 @@
       <c r="O18" s="10"/>
       <c r="P18" s="10"/>
     </row>
-    <row r="19" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>4134</v>
       </c>
@@ -16663,8 +16678,8 @@
         <v>4345</v>
       </c>
     </row>
-    <row r="20" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>1041</v>
       </c>
@@ -16714,7 +16729,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="22" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>1040</v>
       </c>
@@ -16764,8 +16779,8 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="23" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="24" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>387</v>
       </c>
@@ -16815,7 +16830,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="25" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>388</v>
       </c>
@@ -16865,7 +16880,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="26" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>389</v>
       </c>
@@ -16915,7 +16930,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="27" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>390</v>
       </c>
@@ -16965,7 +16980,7 @@
         <v>2227</v>
       </c>
     </row>
-    <row r="28" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>391</v>
       </c>
@@ -17015,7 +17030,7 @@
         <v>2228</v>
       </c>
     </row>
-    <row r="29" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>392</v>
       </c>
@@ -17065,7 +17080,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="30" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>393</v>
       </c>
@@ -17115,7 +17130,7 @@
         <v>2230</v>
       </c>
     </row>
-    <row r="31" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>394</v>
       </c>
@@ -17165,7 +17180,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="32" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>3177</v>
       </c>
@@ -17215,7 +17230,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="33" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>395</v>
       </c>
@@ -17265,7 +17280,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="34" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>396</v>
       </c>
@@ -17315,7 +17330,7 @@
         <v>2233</v>
       </c>
     </row>
-    <row r="35" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>397</v>
       </c>
@@ -17365,7 +17380,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="36" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>2831</v>
       </c>
@@ -17415,7 +17430,7 @@
         <v>2870</v>
       </c>
     </row>
-    <row r="37" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>2833</v>
       </c>
@@ -17465,7 +17480,7 @@
         <v>2871</v>
       </c>
     </row>
-    <row r="38" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>398</v>
       </c>
@@ -17515,7 +17530,7 @@
         <v>2235</v>
       </c>
     </row>
-    <row r="39" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>2832</v>
       </c>
@@ -17565,7 +17580,7 @@
         <v>2872</v>
       </c>
     </row>
-    <row r="40" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>399</v>
       </c>
@@ -17615,7 +17630,7 @@
         <v>2236</v>
       </c>
     </row>
-    <row r="41" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>400</v>
       </c>
@@ -17665,7 +17680,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="42" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>401</v>
       </c>
@@ -17715,7 +17730,7 @@
         <v>2238</v>
       </c>
     </row>
-    <row r="43" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>402</v>
       </c>
@@ -17765,7 +17780,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="44" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>403</v>
       </c>
@@ -17815,7 +17830,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="45" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>404</v>
       </c>
@@ -17865,7 +17880,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="46" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>405</v>
       </c>
@@ -17915,7 +17930,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="47" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>406</v>
       </c>
@@ -17965,7 +17980,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="48" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>407</v>
       </c>
@@ -18015,7 +18030,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="49" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>408</v>
       </c>
@@ -18065,7 +18080,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="50" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>409</v>
       </c>
@@ -18115,7 +18130,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="51" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>410</v>
       </c>
@@ -18165,7 +18180,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="52" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>386</v>
       </c>
@@ -18215,7 +18230,7 @@
         <v>2248</v>
       </c>
     </row>
-    <row r="53" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>2769</v>
       </c>
@@ -18265,7 +18280,7 @@
         <v>2791</v>
       </c>
     </row>
-    <row r="54" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>413</v>
       </c>
@@ -18315,7 +18330,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="55" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>2770</v>
       </c>
@@ -18365,7 +18380,7 @@
         <v>2790</v>
       </c>
     </row>
-    <row r="56" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>2771</v>
       </c>
@@ -18415,7 +18430,7 @@
         <v>2792</v>
       </c>
     </row>
-    <row r="57" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>2772</v>
       </c>
@@ -18465,7 +18480,7 @@
         <v>2793</v>
       </c>
     </row>
-    <row r="58" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>2830</v>
       </c>
@@ -18515,7 +18530,7 @@
         <v>2828</v>
       </c>
     </row>
-    <row r="59" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>412</v>
       </c>
@@ -18565,7 +18580,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>2887</v>
       </c>
@@ -18615,7 +18630,7 @@
         <v>2891</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>2903</v>
       </c>
@@ -18665,7 +18680,7 @@
         <v>2907</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>2919</v>
       </c>
@@ -18715,7 +18730,7 @@
         <v>2923</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>2935</v>
       </c>
@@ -18765,7 +18780,7 @@
         <v>2938</v>
       </c>
     </row>
-    <row r="65" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>4069</v>
       </c>
@@ -18815,7 +18830,7 @@
         <v>4085</v>
       </c>
     </row>
-    <row r="66" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>995</v>
       </c>
@@ -18865,7 +18880,7 @@
         <v>3597</v>
       </c>
     </row>
-    <row r="67" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>996</v>
       </c>
@@ -18915,7 +18930,7 @@
         <v>3598</v>
       </c>
     </row>
-    <row r="68" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>997</v>
       </c>
@@ -18965,7 +18980,7 @@
         <v>3599</v>
       </c>
     </row>
-    <row r="69" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>998</v>
       </c>
@@ -19015,7 +19030,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="71" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>2967</v>
       </c>
@@ -19065,7 +19080,7 @@
         <v>3012</v>
       </c>
     </row>
-    <row r="72" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>2968</v>
       </c>
@@ -19112,7 +19127,7 @@
         <v>3025</v>
       </c>
     </row>
-    <row r="73" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>2969</v>
       </c>
@@ -19162,7 +19177,7 @@
         <v>3020</v>
       </c>
     </row>
-    <row r="74" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>2970</v>
       </c>
@@ -19212,7 +19227,7 @@
         <v>3004</v>
       </c>
     </row>
-    <row r="76" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
         <v>5</v>
       </c>
@@ -19262,7 +19277,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="77" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>3043</v>
       </c>
@@ -19312,7 +19327,7 @@
         <v>3056</v>
       </c>
     </row>
-    <row r="78" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>6</v>
       </c>
@@ -19362,7 +19377,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="79" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>7</v>
       </c>
@@ -19412,7 +19427,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="80" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
         <v>8</v>
       </c>
@@ -19462,7 +19477,7 @@
         <v>2092</v>
       </c>
     </row>
-    <row r="81" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>3628</v>
       </c>
@@ -19512,7 +19527,7 @@
         <v>3766</v>
       </c>
     </row>
-    <row r="82" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>3638</v>
       </c>
@@ -19562,7 +19577,7 @@
         <v>3767</v>
       </c>
     </row>
-    <row r="83" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
         <v>3630</v>
       </c>
@@ -19612,7 +19627,7 @@
         <v>3673</v>
       </c>
     </row>
-    <row r="84" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
         <v>3631</v>
       </c>
@@ -19662,7 +19677,7 @@
         <v>3684</v>
       </c>
     </row>
-    <row r="85" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
         <v>332</v>
       </c>
@@ -19712,7 +19727,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="86" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
         <v>3885</v>
       </c>
@@ -19762,7 +19777,7 @@
         <v>3897</v>
       </c>
     </row>
-    <row r="87" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>334</v>
       </c>
@@ -19812,7 +19827,7 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="88" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
         <v>9</v>
       </c>
@@ -19862,7 +19877,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="89" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>3652</v>
       </c>
@@ -19912,7 +19927,7 @@
         <v>3801</v>
       </c>
     </row>
-    <row r="90" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
         <v>10</v>
       </c>
@@ -19962,8 +19977,8 @@
         <v>2081</v>
       </c>
     </row>
-    <row r="91" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="92" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
         <v>30</v>
       </c>
@@ -20013,7 +20028,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="93" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
         <v>31</v>
       </c>
@@ -20063,7 +20078,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="94" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
         <v>32</v>
       </c>
@@ -20113,7 +20128,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="95" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>33</v>
       </c>
@@ -20163,7 +20178,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="96" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
         <v>34</v>
       </c>
@@ -20213,7 +20228,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="97" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>35</v>
       </c>
@@ -20263,7 +20278,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="98" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
         <v>969</v>
       </c>
@@ -20313,7 +20328,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="99" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
         <v>36</v>
       </c>
@@ -20363,7 +20378,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="100" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A100" s="10" t="s">
         <v>5136</v>
       </c>
@@ -20385,7 +20400,7 @@
       <c r="O100" s="10"/>
       <c r="P100" s="10"/>
     </row>
-    <row r="101" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A101" s="10" t="s">
         <v>5132</v>
       </c>
@@ -20407,7 +20422,7 @@
       <c r="O101" s="10"/>
       <c r="P101" s="10"/>
     </row>
-    <row r="102" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A102" s="10" t="s">
         <v>5133</v>
       </c>
@@ -20429,7 +20444,7 @@
       <c r="O102" s="10"/>
       <c r="P102" s="10"/>
     </row>
-    <row r="103" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
         <v>37</v>
       </c>
@@ -20479,7 +20494,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="104" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A104" s="3" t="s">
         <v>4130</v>
       </c>
@@ -20529,7 +20544,7 @@
         <v>4306</v>
       </c>
     </row>
-    <row r="105" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
         <v>4131</v>
       </c>
@@ -20579,7 +20594,7 @@
         <v>4330</v>
       </c>
     </row>
-    <row r="106" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A106" s="3" t="s">
         <v>4930</v>
       </c>
@@ -20629,7 +20644,7 @@
         <v>4274</v>
       </c>
     </row>
-    <row r="107" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
         <v>4928</v>
       </c>
@@ -20679,8 +20694,8 @@
         <v>4943</v>
       </c>
     </row>
-    <row r="108" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="109" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
         <v>2421</v>
       </c>
@@ -20730,7 +20745,7 @@
         <v>2591</v>
       </c>
     </row>
-    <row r="110" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
         <v>2424</v>
       </c>
@@ -20780,7 +20795,7 @@
         <v>2593</v>
       </c>
     </row>
-    <row r="111" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
         <v>3257</v>
       </c>
@@ -20830,8 +20845,8 @@
         <v>3273</v>
       </c>
     </row>
-    <row r="112" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="113" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
         <v>2885</v>
       </c>
@@ -20881,7 +20896,7 @@
         <v>3040</v>
       </c>
     </row>
-    <row r="114" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A114" s="3" t="s">
         <v>3099</v>
       </c>
@@ -20931,7 +20946,7 @@
         <v>3101</v>
       </c>
     </row>
-    <row r="115" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
         <v>3091</v>
       </c>
@@ -20981,7 +20996,7 @@
         <v>3128</v>
       </c>
     </row>
-    <row r="116" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A116" s="3" t="s">
         <v>3092</v>
       </c>
@@ -21031,7 +21046,7 @@
         <v>3152</v>
       </c>
     </row>
-    <row r="117" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A117" s="3" t="s">
         <v>3093</v>
       </c>
@@ -21081,7 +21096,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="118" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A118" s="3" t="s">
         <v>3096</v>
       </c>
@@ -21131,7 +21146,7 @@
         <v>3155</v>
       </c>
     </row>
-    <row r="119" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
         <v>3059</v>
       </c>
@@ -21181,7 +21196,7 @@
         <v>3066</v>
       </c>
     </row>
-    <row r="120" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A120" s="3" t="s">
         <v>3060</v>
       </c>
@@ -21231,7 +21246,7 @@
         <v>3089</v>
       </c>
     </row>
-    <row r="121" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A121" s="3" t="s">
         <v>4199</v>
       </c>
@@ -21281,8 +21296,8 @@
         <v>4290</v>
       </c>
     </row>
-    <row r="122" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="123" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
         <v>23</v>
       </c>
@@ -21332,7 +21347,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="124" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A124" s="3" t="s">
         <v>11</v>
       </c>
@@ -21382,7 +21397,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="125" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A125" s="3" t="s">
         <v>12</v>
       </c>
@@ -21432,7 +21447,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="126" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A126" s="3" t="s">
         <v>13</v>
       </c>
@@ -21482,7 +21497,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="127" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
         <v>14</v>
       </c>
@@ -21532,7 +21547,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="128" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
         <v>15</v>
       </c>
@@ -21582,7 +21597,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="129" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
         <v>16</v>
       </c>
@@ -21632,7 +21647,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="130" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
         <v>17</v>
       </c>
@@ -21682,7 +21697,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="131" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
         <v>18</v>
       </c>
@@ -21732,7 +21747,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="132" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
         <v>3438</v>
       </c>
@@ -21782,7 +21797,7 @@
         <v>3452</v>
       </c>
     </row>
-    <row r="133" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
         <v>19</v>
       </c>
@@ -21832,7 +21847,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="134" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
         <v>2328</v>
       </c>
@@ -21882,7 +21897,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="135" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
         <v>2346</v>
       </c>
@@ -21932,7 +21947,7 @@
         <v>2354</v>
       </c>
     </row>
-    <row r="136" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A136" s="3" t="s">
         <v>20</v>
       </c>
@@ -21982,7 +21997,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="137" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
         <v>21</v>
       </c>
@@ -22032,7 +22047,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="138" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
         <v>2700</v>
       </c>
@@ -22082,7 +22097,7 @@
         <v>2711</v>
       </c>
     </row>
-    <row r="139" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
         <v>22</v>
       </c>
@@ -22132,7 +22147,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="140" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A140" s="3" t="s">
         <v>24</v>
       </c>
@@ -22182,7 +22197,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="141" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
         <v>25</v>
       </c>
@@ -22232,7 +22247,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="142" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A142" s="3" t="s">
         <v>26</v>
       </c>
@@ -22282,7 +22297,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="143" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
         <v>27</v>
       </c>
@@ -22332,7 +22347,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="144" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A144" s="3" t="s">
         <v>2396</v>
       </c>
@@ -22382,7 +22397,7 @@
         <v>2408</v>
       </c>
     </row>
-    <row r="145" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A145" s="3" t="s">
         <v>2704</v>
       </c>
@@ -22432,7 +22447,7 @@
         <v>2731</v>
       </c>
     </row>
-    <row r="146" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A146" s="3" t="s">
         <v>2705</v>
       </c>
@@ -22482,7 +22497,7 @@
         <v>2738</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>2950</v>
       </c>
@@ -22532,7 +22547,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="148" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A148" s="3" t="s">
         <v>4001</v>
       </c>
@@ -22582,7 +22597,7 @@
         <v>4012</v>
       </c>
     </row>
-    <row r="149" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A149" s="3" t="s">
         <v>4005</v>
       </c>
@@ -22632,7 +22647,7 @@
         <v>4046</v>
       </c>
     </row>
-    <row r="150" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A150" s="3" t="s">
         <v>4002</v>
       </c>
@@ -22682,7 +22697,7 @@
         <v>4045</v>
       </c>
     </row>
-    <row r="151" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A151" s="3" t="s">
         <v>2606</v>
       </c>
@@ -22732,7 +22747,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="152" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A152" s="3" t="s">
         <v>28</v>
       </c>
@@ -22782,7 +22797,7 @@
         <v>2046</v>
       </c>
     </row>
-    <row r="153" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A153" s="3" t="s">
         <v>29</v>
       </c>
@@ -22832,7 +22847,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="154" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A154" s="3" t="s">
         <v>982</v>
       </c>
@@ -22882,7 +22897,7 @@
         <v>3455</v>
       </c>
     </row>
-    <row r="155" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A155" s="3" t="s">
         <v>978</v>
       </c>
@@ -22932,7 +22947,7 @@
         <v>3475</v>
       </c>
     </row>
-    <row r="156" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A156" s="3" t="s">
         <v>4086</v>
       </c>
@@ -22982,7 +22997,7 @@
         <v>4090</v>
       </c>
     </row>
-    <row r="157" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A157" s="3" t="s">
         <v>979</v>
       </c>
@@ -23032,7 +23047,7 @@
         <v>3476</v>
       </c>
     </row>
-    <row r="158" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A158" s="3" t="s">
         <v>980</v>
       </c>
@@ -23082,7 +23097,7 @@
         <v>3835</v>
       </c>
     </row>
-    <row r="159" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A159" s="3" t="s">
         <v>986</v>
       </c>
@@ -23132,7 +23147,7 @@
         <v>3529</v>
       </c>
     </row>
-    <row r="160" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A160" s="3" t="s">
         <v>981</v>
       </c>
@@ -23182,7 +23197,7 @@
         <v>3530</v>
       </c>
     </row>
-    <row r="161" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A161" s="3" t="s">
         <v>4087</v>
       </c>
@@ -23232,8 +23247,8 @@
         <v>4122</v>
       </c>
     </row>
-    <row r="162" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="163" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A163" s="3" t="s">
         <v>2594</v>
       </c>
@@ -23283,7 +23298,7 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="164" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A164" s="3" t="s">
         <v>2595</v>
       </c>
@@ -23333,7 +23348,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="165" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A165" s="3" t="s">
         <v>2596</v>
       </c>
@@ -23383,7 +23398,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="166" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A166" s="3" t="s">
         <v>2597</v>
       </c>
@@ -23433,7 +23448,7 @@
         <v>2625</v>
       </c>
     </row>
-    <row r="167" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A167" s="3" t="s">
         <v>2598</v>
       </c>
@@ -23483,7 +23498,7 @@
         <v>2626</v>
       </c>
     </row>
-    <row r="168" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A168" s="3" t="s">
         <v>2599</v>
       </c>
@@ -23533,7 +23548,7 @@
         <v>2627</v>
       </c>
     </row>
-    <row r="170" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A170" s="3" t="s">
         <v>1242</v>
       </c>
@@ -23583,7 +23598,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="171" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A171" s="3" t="s">
         <v>1213</v>
       </c>
@@ -23633,7 +23648,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="172" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A172" s="3" t="s">
         <v>1214</v>
       </c>
@@ -23683,7 +23698,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="173" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A173" s="3" t="s">
         <v>5021</v>
       </c>
@@ -23733,7 +23748,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="174" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A174" s="3" t="s">
         <v>1202</v>
       </c>
@@ -23783,7 +23798,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="175" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A175" s="3" t="s">
         <v>1203</v>
       </c>
@@ -23833,7 +23848,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="176" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A176" s="3" t="s">
         <v>1210</v>
       </c>
@@ -23883,7 +23898,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="177" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A177" s="3" t="s">
         <v>1204</v>
       </c>
@@ -23933,7 +23948,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="178" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A178" s="3" t="s">
         <v>1205</v>
       </c>
@@ -23983,7 +23998,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="179" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A179" s="3" t="s">
         <v>1215</v>
       </c>
@@ -24033,7 +24048,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="180" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A180" s="3" t="s">
         <v>1216</v>
       </c>
@@ -24083,7 +24098,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="181" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A181" s="3" t="s">
         <v>1217</v>
       </c>
@@ -24133,7 +24148,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="182" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A182" s="3" t="s">
         <v>1222</v>
       </c>
@@ -24183,7 +24198,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="183" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A183" s="3" t="s">
         <v>1223</v>
       </c>
@@ -24233,7 +24248,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="184" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A184" s="3" t="s">
         <v>2364</v>
       </c>
@@ -24283,7 +24298,7 @@
         <v>2367</v>
       </c>
     </row>
-    <row r="185" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A185" s="3" t="s">
         <v>2750</v>
       </c>
@@ -24333,7 +24348,7 @@
         <v>2757</v>
       </c>
     </row>
-    <row r="186" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A186" s="3" t="s">
         <v>1227</v>
       </c>
@@ -24383,7 +24398,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="187" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A187" s="3" t="s">
         <v>1240</v>
       </c>
@@ -24433,7 +24448,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="188" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A188" s="3" t="s">
         <v>1241</v>
       </c>
@@ -24474,7 +24489,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="189" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A189" s="3" t="s">
         <v>1232</v>
       </c>
@@ -24524,7 +24539,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="190" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A190" s="3" t="s">
         <v>1233</v>
       </c>
@@ -24574,7 +24589,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="191" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A191" s="3" t="s">
         <v>1230</v>
       </c>
@@ -24624,7 +24639,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="192" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A192" s="3" t="s">
         <v>1231</v>
       </c>
@@ -24674,7 +24689,7 @@
         <v>2121</v>
       </c>
     </row>
-    <row r="193" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A193" s="3" t="s">
         <v>1238</v>
       </c>
@@ -24724,7 +24739,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="194" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A194" s="3" t="s">
         <v>5026</v>
       </c>
@@ -24774,7 +24789,7 @@
         <v>5028</v>
       </c>
     </row>
-    <row r="195" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A195" s="3" t="s">
         <v>5022</v>
       </c>
@@ -24824,7 +24839,7 @@
         <v>5052</v>
       </c>
     </row>
-    <row r="196" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A196" s="3" t="s">
         <v>5023</v>
       </c>
@@ -24874,8 +24889,8 @@
         <v>5053</v>
       </c>
     </row>
-    <row r="197" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="198" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A198" s="3" t="s">
         <v>1192</v>
       </c>
@@ -24925,7 +24940,7 @@
         <v>2141</v>
       </c>
     </row>
-    <row r="199" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A199" s="3" t="s">
         <v>1038</v>
       </c>
@@ -24975,7 +24990,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="200" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A200" s="3" t="s">
         <v>1044</v>
       </c>
@@ -25025,7 +25040,7 @@
         <v>2143</v>
       </c>
     </row>
-    <row r="201" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A201" s="3" t="s">
         <v>5067</v>
       </c>
@@ -25075,7 +25090,7 @@
         <v>5073</v>
       </c>
     </row>
-    <row r="202" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A202" s="3" t="s">
         <v>1193</v>
       </c>
@@ -25125,7 +25140,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="203" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A203" s="3" t="s">
         <v>1194</v>
       </c>
@@ -25175,7 +25190,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="204" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A204" s="3" t="s">
         <v>1199</v>
       </c>
@@ -25225,7 +25240,7 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="205" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A205" s="3" t="s">
         <v>1046</v>
       </c>
@@ -25275,7 +25290,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="206" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A206" s="3" t="s">
         <v>1047</v>
       </c>
@@ -25325,7 +25340,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="207" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A207" s="3" t="s">
         <v>1051</v>
       </c>
@@ -25375,7 +25390,7 @@
         <v>2149</v>
       </c>
     </row>
-    <row r="208" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A208" s="3" t="s">
         <v>2767</v>
       </c>
@@ -25425,7 +25440,7 @@
         <v>2757</v>
       </c>
     </row>
-    <row r="209" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A209" s="3" t="s">
         <v>1183</v>
       </c>
@@ -25475,7 +25490,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="210" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A210" s="3" t="s">
         <v>1020</v>
       </c>
@@ -25525,7 +25540,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="211" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A211" s="3" t="s">
         <v>1021</v>
       </c>
@@ -25575,7 +25590,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="212" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A212" s="3" t="s">
         <v>1024</v>
       </c>
@@ -25625,7 +25640,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="213" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A213" s="3" t="s">
         <v>1025</v>
       </c>
@@ -25675,7 +25690,7 @@
         <v>2161</v>
       </c>
     </row>
-    <row r="214" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A214" s="3" t="s">
         <v>1029</v>
       </c>
@@ -25725,7 +25740,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="215" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A215" s="3" t="s">
         <v>1030</v>
       </c>
@@ -25775,7 +25790,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="216" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A216" s="3" t="s">
         <v>1031</v>
       </c>
@@ -25825,7 +25840,7 @@
         <v>2163</v>
       </c>
     </row>
-    <row r="217" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A217" s="3" t="s">
         <v>1189</v>
       </c>
@@ -25872,7 +25887,7 @@
         <v>2164</v>
       </c>
     </row>
-    <row r="218" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A218" s="3" t="s">
         <v>1188</v>
       </c>
@@ -25919,7 +25934,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="219" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A219" s="3" t="s">
         <v>1053</v>
       </c>
@@ -25969,7 +25984,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="220" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A220" s="3" t="s">
         <v>1186</v>
       </c>
@@ -26016,7 +26031,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="221" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A221" s="3" t="s">
         <v>1187</v>
       </c>
@@ -26063,8 +26078,8 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="222" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="223" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="223" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A223" s="3" t="s">
         <v>4136</v>
       </c>
@@ -26114,7 +26129,7 @@
         <v>4274</v>
       </c>
     </row>
-    <row r="224" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A224" s="3" t="s">
         <v>1004</v>
       </c>
@@ -26164,7 +26179,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="225" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A225" s="3" t="s">
         <v>1005</v>
       </c>
@@ -26214,7 +26229,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="226" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A226" s="3" t="s">
         <v>1006</v>
       </c>
@@ -26264,7 +26279,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="227" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A227" s="3" t="s">
         <v>1015</v>
       </c>
@@ -26314,7 +26329,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="228" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A228" s="3" t="s">
         <v>1007</v>
       </c>
@@ -26364,7 +26379,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="229" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A229" s="3" t="s">
         <v>1016</v>
       </c>
@@ -26414,7 +26429,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A230" s="3" t="s">
         <v>2326</v>
       </c>
@@ -26464,7 +26479,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="231" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A231" s="3" t="s">
         <v>2327</v>
       </c>
@@ -26514,7 +26529,7 @@
         <v>2308</v>
       </c>
     </row>
-    <row r="232" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A232" s="3" t="s">
         <v>1008</v>
       </c>
@@ -26564,7 +26579,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="233" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A233" s="3" t="s">
         <v>1010</v>
       </c>
@@ -26614,7 +26629,7 @@
         <v>2179</v>
       </c>
     </row>
-    <row r="234" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A234" s="3" t="s">
         <v>1009</v>
       </c>
@@ -26664,7 +26679,7 @@
         <v>2178</v>
       </c>
     </row>
-    <row r="235" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A235" s="3" t="s">
         <v>4047</v>
       </c>
@@ -26714,7 +26729,7 @@
         <v>4055</v>
       </c>
     </row>
-    <row r="236" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A236" s="3" t="s">
         <v>4049</v>
       </c>
@@ -26764,7 +26779,7 @@
         <v>4051</v>
       </c>
     </row>
-    <row r="237" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A237" s="3" t="s">
         <v>4050</v>
       </c>
@@ -26814,7 +26829,7 @@
         <v>4052</v>
       </c>
     </row>
-    <row r="238" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A238" s="3" t="s">
         <v>4053</v>
       </c>
@@ -26864,7 +26879,7 @@
         <v>4054</v>
       </c>
     </row>
-    <row r="239" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A239" s="3" t="s">
         <v>3841</v>
       </c>
@@ -26914,7 +26929,7 @@
         <v>3884</v>
       </c>
     </row>
-    <row r="240" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A240" s="3" t="s">
         <v>3842</v>
       </c>
@@ -26964,7 +26979,7 @@
         <v>3883</v>
       </c>
     </row>
-    <row r="241" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A241" s="3" t="s">
         <v>3843</v>
       </c>
@@ -27014,7 +27029,7 @@
         <v>3882</v>
       </c>
     </row>
-    <row r="242" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A242" s="3" t="s">
         <v>3901</v>
       </c>
@@ -27064,7 +27079,7 @@
         <v>3909</v>
       </c>
     </row>
-    <row r="243" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A243" s="3" t="s">
         <v>3902</v>
       </c>
@@ -27114,7 +27129,7 @@
         <v>3910</v>
       </c>
     </row>
-    <row r="244" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A244" s="3" t="s">
         <v>3903</v>
       </c>
@@ -27164,7 +27179,7 @@
         <v>3911</v>
       </c>
     </row>
-    <row r="245" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A245" s="3" t="s">
         <v>4123</v>
       </c>
@@ -27214,7 +27229,7 @@
         <v>3897</v>
       </c>
     </row>
-    <row r="246" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A246" s="3" t="s">
         <v>4129</v>
       </c>
@@ -27264,7 +27279,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="247" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A247" s="3" t="s">
         <v>5083</v>
       </c>
@@ -27314,7 +27329,7 @@
         <v>5108</v>
       </c>
     </row>
-    <row r="248" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A248" s="3" t="s">
         <v>5084</v>
       </c>
@@ -27364,7 +27379,7 @@
         <v>5107</v>
       </c>
     </row>
-    <row r="249" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A249" s="3" t="s">
         <v>5066</v>
       </c>
@@ -27414,7 +27429,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="250" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A250" s="3" t="s">
         <v>4125</v>
       </c>
@@ -27464,7 +27479,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="251" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A251" s="3" t="s">
         <v>4126</v>
       </c>
@@ -27514,7 +27529,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="252" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A252" s="3" t="s">
         <v>1011</v>
       </c>
@@ -27564,7 +27579,7 @@
         <v>2180</v>
       </c>
     </row>
-    <row r="253" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A253" s="3" t="s">
         <v>3226</v>
       </c>
@@ -27614,7 +27629,7 @@
         <v>3246</v>
       </c>
     </row>
-    <row r="254" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A254" s="3" t="s">
         <v>3225</v>
       </c>
@@ -27664,7 +27679,7 @@
         <v>3241</v>
       </c>
     </row>
-    <row r="255" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A255" s="3" t="s">
         <v>5088</v>
       </c>
@@ -27714,7 +27729,7 @@
         <v>5130</v>
       </c>
     </row>
-    <row r="256" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A256" s="3" t="s">
         <v>1012</v>
       </c>
@@ -27764,7 +27779,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="257" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A257" s="3" t="s">
         <v>3289</v>
       </c>
@@ -27814,7 +27829,7 @@
         <v>3304</v>
       </c>
     </row>
-    <row r="258" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A258" s="3" t="s">
         <v>3290</v>
       </c>
@@ -27864,7 +27879,7 @@
         <v>3310</v>
       </c>
     </row>
-    <row r="259" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A259" s="3" t="s">
         <v>4138</v>
       </c>
@@ -27914,7 +27929,7 @@
         <v>2092</v>
       </c>
     </row>
-    <row r="260" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A260" s="3" t="s">
         <v>1013</v>
       </c>
@@ -27964,7 +27979,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="261" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A261" s="3" t="s">
         <v>1014</v>
       </c>
@@ -28014,7 +28029,7 @@
         <v>2092</v>
       </c>
     </row>
-    <row r="262" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A262" s="3" t="s">
         <v>1017</v>
       </c>
@@ -28064,7 +28079,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="263" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A263" s="3" t="s">
         <v>1036</v>
       </c>
@@ -28114,7 +28129,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="264" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A264" s="3" t="s">
         <v>3195</v>
       </c>
@@ -28164,7 +28179,7 @@
         <v>3222</v>
       </c>
     </row>
-    <row r="265" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A265" s="3" t="s">
         <v>4200</v>
       </c>
@@ -28214,7 +28229,7 @@
         <v>4255</v>
       </c>
     </row>
-    <row r="267" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A267" s="3" t="s">
         <v>439</v>
       </c>
@@ -28264,7 +28279,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="268" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A268" s="3" t="s">
         <v>440</v>
       </c>
@@ -28314,7 +28329,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="269" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A269" s="3" t="s">
         <v>441</v>
       </c>
@@ -28364,7 +28379,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="270" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A270" s="3" t="s">
         <v>442</v>
       </c>
@@ -28414,7 +28429,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="271" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A271" s="3" t="s">
         <v>443</v>
       </c>
@@ -28464,7 +28479,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="272" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A272" s="3" t="s">
         <v>444</v>
       </c>
@@ -28514,7 +28529,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="273" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A273" s="3" t="s">
         <v>445</v>
       </c>
@@ -28564,7 +28579,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="274" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A274" s="3" t="s">
         <v>446</v>
       </c>
@@ -28614,7 +28629,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="275" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A275" s="3" t="s">
         <v>3440</v>
       </c>
@@ -28664,7 +28679,7 @@
         <v>3452</v>
       </c>
     </row>
-    <row r="276" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A276" s="3" t="s">
         <v>695</v>
       </c>
@@ -28714,7 +28729,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="277" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A277" s="3" t="s">
         <v>2329</v>
       </c>
@@ -28764,7 +28779,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="278" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A278" s="3" t="s">
         <v>2349</v>
       </c>
@@ -28814,7 +28829,7 @@
         <v>2354</v>
       </c>
     </row>
-    <row r="279" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A279" s="3" t="s">
         <v>1197</v>
       </c>
@@ -28864,7 +28879,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="280" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A280" s="3" t="s">
         <v>1221</v>
       </c>
@@ -28914,7 +28929,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="281" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A281" s="3" t="s">
         <v>1037</v>
       </c>
@@ -28964,8 +28979,8 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="282" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="283" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="283" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A283" s="3" t="s">
         <v>691</v>
       </c>
@@ -29015,7 +29030,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="284" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A284" s="3" t="s">
         <v>3193</v>
       </c>
@@ -29065,7 +29080,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="285" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A285" s="3" t="s">
         <v>3194</v>
       </c>
@@ -29115,10 +29130,10 @@
         <v>3207</v>
       </c>
     </row>
-    <row r="286" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="J286" s="4"/>
     </row>
-    <row r="287" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A287" s="3" t="s">
         <v>459</v>
       </c>
@@ -29168,7 +29183,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="288" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A288" s="3" t="s">
         <v>460</v>
       </c>
@@ -29218,7 +29233,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="289" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A289" s="3" t="s">
         <v>461</v>
       </c>
@@ -29268,7 +29283,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="290" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A290" s="3" t="s">
         <v>476</v>
       </c>
@@ -29318,7 +29333,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="291" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A291" s="3" t="s">
         <v>2330</v>
       </c>
@@ -29368,7 +29383,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="292" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A292" s="3" t="s">
         <v>2348</v>
       </c>
@@ -29418,7 +29433,7 @@
         <v>2354</v>
       </c>
     </row>
-    <row r="293" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A293" s="3" t="s">
         <v>1027</v>
       </c>
@@ -29468,7 +29483,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="294" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A294" s="3" t="s">
         <v>462</v>
       </c>
@@ -29518,7 +29533,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="295" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A295" s="3" t="s">
         <v>463</v>
       </c>
@@ -29568,7 +29583,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="296" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A296" s="3" t="s">
         <v>464</v>
       </c>
@@ -29618,7 +29633,7 @@
         <v>2278</v>
       </c>
     </row>
-    <row r="297" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A297" s="3" t="s">
         <v>465</v>
       </c>
@@ -29668,7 +29683,7 @@
         <v>2279</v>
       </c>
     </row>
-    <row r="298" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A298" s="3" t="s">
         <v>466</v>
       </c>
@@ -29718,7 +29733,7 @@
         <v>2280</v>
       </c>
     </row>
-    <row r="299" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A299" s="3" t="s">
         <v>467</v>
       </c>
@@ -29768,7 +29783,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="300" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A300" s="3" t="s">
         <v>468</v>
       </c>
@@ -29818,7 +29833,7 @@
         <v>2282</v>
       </c>
     </row>
-    <row r="301" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A301" s="3" t="s">
         <v>469</v>
       </c>
@@ -29868,7 +29883,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="302" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A302" s="3" t="s">
         <v>470</v>
       </c>
@@ -29918,7 +29933,7 @@
         <v>2284</v>
       </c>
     </row>
-    <row r="303" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A303" s="3" t="s">
         <v>471</v>
       </c>
@@ -29968,7 +29983,7 @@
         <v>2285</v>
       </c>
     </row>
-    <row r="304" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A304" s="3" t="s">
         <v>472</v>
       </c>
@@ -30018,7 +30033,7 @@
         <v>2286</v>
       </c>
     </row>
-    <row r="305" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A305" s="3" t="s">
         <v>473</v>
       </c>
@@ -30068,7 +30083,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="306" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A306" s="3" t="s">
         <v>474</v>
       </c>
@@ -30118,7 +30133,7 @@
         <v>2288</v>
       </c>
     </row>
-    <row r="307" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A307" s="3" t="s">
         <v>475</v>
       </c>
@@ -30168,7 +30183,7 @@
         <v>2289</v>
       </c>
     </row>
-    <row r="308" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A308" s="3" t="s">
         <v>701</v>
       </c>
@@ -30218,7 +30233,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="309" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A309" s="3" t="s">
         <v>702</v>
       </c>
@@ -30268,7 +30283,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="310" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A310" s="3" t="s">
         <v>703</v>
       </c>
@@ -30318,7 +30333,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="311" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A311" s="3" t="s">
         <v>704</v>
       </c>
@@ -30368,7 +30383,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="312" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A312" s="3" t="s">
         <v>705</v>
       </c>
@@ -30418,7 +30433,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="313" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A313" s="3" t="s">
         <v>706</v>
       </c>
@@ -30468,7 +30483,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="314" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A314" s="3" t="s">
         <v>707</v>
       </c>
@@ -30518,7 +30533,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="315" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A315" s="3" t="s">
         <v>708</v>
       </c>
@@ -30568,7 +30583,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="316" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A316" s="3" t="s">
         <v>709</v>
       </c>
@@ -30618,7 +30633,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="317" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A317" s="3" t="s">
         <v>710</v>
       </c>
@@ -30668,7 +30683,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="318" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A318" s="3" t="s">
         <v>711</v>
       </c>
@@ -30718,7 +30733,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="319" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A319" s="3" t="s">
         <v>712</v>
       </c>
@@ -30768,7 +30783,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="320" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A320" s="3" t="s">
         <v>3435</v>
       </c>
@@ -30818,7 +30833,7 @@
         <v>3475</v>
       </c>
     </row>
-    <row r="321" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A321" s="3" t="s">
         <v>3436</v>
       </c>
@@ -30868,8 +30883,8 @@
         <v>3499</v>
       </c>
     </row>
-    <row r="322" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="323" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="323" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A323" s="3" t="s">
         <v>987</v>
       </c>
@@ -30919,7 +30934,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="324" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A324" s="3" t="s">
         <v>988</v>
       </c>
@@ -30969,7 +30984,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="325" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A325" s="3" t="s">
         <v>989</v>
       </c>
@@ -31019,7 +31034,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="326" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A326" s="3" t="s">
         <v>990</v>
       </c>
@@ -31069,8 +31084,8 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="327" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="328" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="328" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A328" s="3" t="s">
         <v>4724</v>
       </c>
@@ -31120,7 +31135,7 @@
         <v>4760</v>
       </c>
     </row>
-    <row r="329" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A329" s="3" t="s">
         <v>4727</v>
       </c>
@@ -31170,7 +31185,7 @@
         <v>4773</v>
       </c>
     </row>
-    <row r="330" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A330" s="3" t="s">
         <v>4725</v>
       </c>
@@ -31220,3963 +31235,4057 @@
         <v>4787</v>
       </c>
     </row>
-    <row r="331" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A331" s="3" t="s">
+    <row r="331" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A331" s="10" t="s">
+        <v>5139</v>
+      </c>
+      <c r="B331" s="10" t="s">
+        <v>5140</v>
+      </c>
+      <c r="C331" s="10"/>
+      <c r="D331" s="10"/>
+      <c r="E331" s="10"/>
+      <c r="F331" s="10"/>
+      <c r="G331" s="10"/>
+      <c r="H331" s="10"/>
+      <c r="I331" s="10"/>
+      <c r="J331" s="10"/>
+      <c r="K331" s="10"/>
+      <c r="L331" s="10"/>
+      <c r="M331" s="10"/>
+      <c r="N331" s="10"/>
+      <c r="O331" s="10"/>
+      <c r="P331" s="10"/>
+    </row>
+    <row r="332" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A332" s="3" t="s">
         <v>4726</v>
       </c>
-      <c r="B331" s="3" t="s">
+      <c r="B332" s="3" t="s">
         <v>4736</v>
       </c>
-      <c r="C331" s="3" t="s">
+      <c r="C332" s="3" t="s">
         <v>4788</v>
       </c>
-      <c r="D331" s="3" t="s">
+      <c r="D332" s="3" t="s">
         <v>4789</v>
       </c>
-      <c r="E331" s="3" t="s">
+      <c r="E332" s="3" t="s">
         <v>4790</v>
       </c>
-      <c r="F331" s="3" t="s">
+      <c r="F332" s="3" t="s">
         <v>4791</v>
       </c>
-      <c r="G331" s="3" t="s">
+      <c r="G332" s="3" t="s">
         <v>4792</v>
       </c>
-      <c r="H331" s="3" t="s">
+      <c r="H332" s="3" t="s">
         <v>4793</v>
       </c>
-      <c r="I331" s="3" t="s">
+      <c r="I332" s="3" t="s">
         <v>4794</v>
       </c>
-      <c r="J331" s="3" t="s">
+      <c r="J332" s="3" t="s">
         <v>4795</v>
       </c>
-      <c r="K331" s="3" t="s">
+      <c r="K332" s="3" t="s">
         <v>4796</v>
       </c>
-      <c r="L331" s="3" t="s">
+      <c r="L332" s="3" t="s">
         <v>4797</v>
       </c>
-      <c r="M331" s="3" t="s">
+      <c r="M332" s="3" t="s">
         <v>4798</v>
       </c>
-      <c r="N331" s="3" t="s">
+      <c r="N332" s="3" t="s">
         <v>4799</v>
       </c>
-      <c r="O331" s="3" t="s">
+      <c r="O332" s="3" t="s">
         <v>4800</v>
       </c>
-      <c r="P331" s="3" t="s">
+      <c r="P332" s="3" t="s">
         <v>4801</v>
       </c>
     </row>
-    <row r="332" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A332" s="3" t="s">
+    <row r="333" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A333" s="3" t="s">
         <v>4728</v>
       </c>
-      <c r="B332" s="3" t="s">
+      <c r="B333" s="3" t="s">
         <v>4735</v>
       </c>
-      <c r="C332" s="3" t="s">
+      <c r="C333" s="3" t="s">
         <v>4802</v>
       </c>
-      <c r="D332" s="3" t="s">
+      <c r="D333" s="3" t="s">
         <v>4803</v>
       </c>
-      <c r="E332" s="3" t="s">
+      <c r="E333" s="3" t="s">
         <v>4804</v>
       </c>
-      <c r="F332" s="3" t="s">
+      <c r="F333" s="3" t="s">
         <v>4805</v>
       </c>
-      <c r="G332" s="3" t="s">
+      <c r="G333" s="3" t="s">
         <v>4806</v>
       </c>
-      <c r="H332" s="3" t="s">
+      <c r="H333" s="3" t="s">
         <v>4735</v>
       </c>
-      <c r="I332" s="3" t="s">
+      <c r="I333" s="3" t="s">
         <v>4807</v>
       </c>
-      <c r="J332" s="3" t="s">
+      <c r="J333" s="3" t="s">
         <v>4808</v>
       </c>
-      <c r="K332" s="3" t="s">
+      <c r="K333" s="3" t="s">
         <v>4809</v>
       </c>
-      <c r="L332" s="3" t="s">
+      <c r="L333" s="3" t="s">
         <v>4810</v>
       </c>
-      <c r="M332" s="3" t="s">
+      <c r="M333" s="3" t="s">
         <v>4806</v>
       </c>
-      <c r="N332" s="3" t="s">
+      <c r="N333" s="3" t="s">
         <v>4811</v>
       </c>
-      <c r="O332" s="3" t="s">
+      <c r="O333" s="3" t="s">
         <v>4812</v>
       </c>
-      <c r="P332" s="3" t="s">
+      <c r="P333" s="3" t="s">
         <v>4813</v>
       </c>
     </row>
-    <row r="333" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A333" s="3" t="s">
+    <row r="334" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A334" s="3" t="s">
         <v>4730</v>
       </c>
-      <c r="B333" s="3" t="s">
+      <c r="B334" s="3" t="s">
         <v>4738</v>
       </c>
-      <c r="C333" s="3" t="s">
+      <c r="C334" s="3" t="s">
         <v>4815</v>
       </c>
-      <c r="D333" s="3" t="s">
+      <c r="D334" s="3" t="s">
         <v>4816</v>
       </c>
-      <c r="E333" s="3" t="s">
+      <c r="E334" s="3" t="s">
         <v>4817</v>
       </c>
-      <c r="F333" s="3" t="s">
+      <c r="F334" s="3" t="s">
         <v>4818</v>
       </c>
-      <c r="G333" s="3" t="s">
+      <c r="G334" s="3" t="s">
         <v>4819</v>
       </c>
-      <c r="H333" s="3" t="s">
+      <c r="H334" s="3" t="s">
         <v>4820</v>
       </c>
-      <c r="I333" s="3" t="s">
+      <c r="I334" s="3" t="s">
         <v>4821</v>
       </c>
-      <c r="J333" s="3" t="s">
+      <c r="J334" s="3" t="s">
         <v>4822</v>
       </c>
-      <c r="K333" s="3" t="s">
+      <c r="K334" s="3" t="s">
         <v>4823</v>
       </c>
-      <c r="L333" s="3" t="s">
+      <c r="L334" s="3" t="s">
         <v>4824</v>
       </c>
-      <c r="M333" s="3" t="s">
+      <c r="M334" s="3" t="s">
         <v>4825</v>
       </c>
-      <c r="N333" s="3" t="s">
+      <c r="N334" s="3" t="s">
         <v>4826</v>
       </c>
-      <c r="O333" s="3" t="s">
+      <c r="O334" s="3" t="s">
         <v>4827</v>
       </c>
-      <c r="P333" s="3" t="s">
+      <c r="P334" s="3" t="s">
         <v>4814</v>
       </c>
     </row>
-    <row r="334" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A334" s="3" t="s">
+    <row r="335" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A335" s="3" t="s">
         <v>4729</v>
       </c>
-      <c r="B334" s="3" t="s">
+      <c r="B335" s="3" t="s">
         <v>4739</v>
       </c>
-      <c r="C334" s="3" t="s">
+      <c r="C335" s="3" t="s">
         <v>4828</v>
       </c>
-      <c r="D334" s="3" t="s">
+      <c r="D335" s="3" t="s">
         <v>4829</v>
       </c>
-      <c r="E334" s="3" t="s">
+      <c r="E335" s="3" t="s">
         <v>4830</v>
       </c>
-      <c r="F334" s="3" t="s">
+      <c r="F335" s="3" t="s">
         <v>4831</v>
       </c>
-      <c r="G334" s="3" t="s">
+      <c r="G335" s="3" t="s">
         <v>4832</v>
       </c>
-      <c r="H334" s="3" t="s">
+      <c r="H335" s="3" t="s">
         <v>4833</v>
       </c>
-      <c r="I334" s="3" t="s">
+      <c r="I335" s="3" t="s">
         <v>4834</v>
       </c>
-      <c r="J334" s="3" t="s">
+      <c r="J335" s="3" t="s">
         <v>4835</v>
       </c>
-      <c r="K334" s="3" t="s">
+      <c r="K335" s="3" t="s">
         <v>4836</v>
       </c>
-      <c r="L334" s="3" t="s">
+      <c r="L335" s="3" t="s">
         <v>4837</v>
       </c>
-      <c r="M334" s="3" t="s">
+      <c r="M335" s="3" t="s">
         <v>4838</v>
       </c>
-      <c r="N334" s="3" t="s">
+      <c r="N335" s="3" t="s">
         <v>4839</v>
       </c>
-      <c r="O334" s="3" t="s">
+      <c r="O335" s="3" t="s">
         <v>4840</v>
       </c>
-      <c r="P334" s="3" t="s">
+      <c r="P335" s="3" t="s">
         <v>4841</v>
       </c>
     </row>
-    <row r="335" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A335" s="3" t="s">
+    <row r="336" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A336" s="3" t="s">
         <v>4731</v>
       </c>
-      <c r="B335" s="3" t="s">
+      <c r="B336" s="3" t="s">
         <v>4740</v>
       </c>
-      <c r="C335" s="3" t="s">
+      <c r="C336" s="3" t="s">
         <v>4842</v>
       </c>
-      <c r="D335" s="3" t="s">
+      <c r="D336" s="3" t="s">
         <v>4843</v>
       </c>
-      <c r="E335" s="3" t="s">
+      <c r="E336" s="3" t="s">
         <v>4844</v>
       </c>
-      <c r="F335" s="3" t="s">
+      <c r="F336" s="3" t="s">
         <v>4845</v>
       </c>
-      <c r="G335" s="3" t="s">
+      <c r="G336" s="3" t="s">
         <v>4846</v>
       </c>
-      <c r="H335" s="3" t="s">
+      <c r="H336" s="3" t="s">
         <v>4847</v>
       </c>
-      <c r="I335" s="3" t="s">
+      <c r="I336" s="3" t="s">
         <v>4848</v>
       </c>
-      <c r="J335" s="3" t="s">
+      <c r="J336" s="3" t="s">
         <v>4849</v>
       </c>
-      <c r="K335" s="3" t="s">
+      <c r="K336" s="3" t="s">
         <v>4850</v>
       </c>
-      <c r="L335" s="3" t="s">
+      <c r="L336" s="3" t="s">
         <v>4851</v>
       </c>
-      <c r="M335" s="3" t="s">
+      <c r="M336" s="3" t="s">
         <v>4852</v>
       </c>
-      <c r="N335" s="3" t="s">
+      <c r="N336" s="3" t="s">
         <v>4853</v>
       </c>
-      <c r="O335" s="3" t="s">
+      <c r="O336" s="3" t="s">
         <v>4854</v>
       </c>
-      <c r="P335" s="3" t="s">
+      <c r="P336" s="3" t="s">
         <v>4855</v>
       </c>
     </row>
-    <row r="336" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A336" s="3" t="s">
+    <row r="337" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A337" s="3" t="s">
         <v>4732</v>
       </c>
-      <c r="B336" s="3" t="s">
+      <c r="B337" s="3" t="s">
         <v>4741</v>
       </c>
-      <c r="C336" s="3" t="s">
+      <c r="C337" s="3" t="s">
         <v>4856</v>
       </c>
-      <c r="D336" s="3" t="s">
+      <c r="D337" s="3" t="s">
         <v>4857</v>
       </c>
-      <c r="E336" s="3" t="s">
+      <c r="E337" s="3" t="s">
         <v>4858</v>
       </c>
-      <c r="F336" s="3" t="s">
+      <c r="F337" s="3" t="s">
         <v>4859</v>
       </c>
-      <c r="G336" s="3" t="s">
+      <c r="G337" s="3" t="s">
         <v>4860</v>
       </c>
-      <c r="H336" s="3" t="s">
+      <c r="H337" s="3" t="s">
         <v>4861</v>
       </c>
-      <c r="I336" s="3" t="s">
+      <c r="I337" s="3" t="s">
         <v>4862</v>
       </c>
-      <c r="J336" s="3" t="s">
+      <c r="J337" s="3" t="s">
         <v>4863</v>
       </c>
-      <c r="K336" s="3" t="s">
+      <c r="K337" s="3" t="s">
         <v>4864</v>
       </c>
-      <c r="L336" s="3" t="s">
+      <c r="L337" s="3" t="s">
         <v>4865</v>
       </c>
-      <c r="M336" s="3" t="s">
+      <c r="M337" s="3" t="s">
         <v>4866</v>
       </c>
-      <c r="N336" s="3" t="s">
+      <c r="N337" s="3" t="s">
         <v>4867</v>
       </c>
-      <c r="O336" s="3" t="s">
+      <c r="O337" s="3" t="s">
         <v>4868</v>
       </c>
-      <c r="P336" s="3" t="s">
+      <c r="P337" s="3" t="s">
         <v>4869</v>
       </c>
     </row>
-    <row r="337" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="338" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A338" s="3" t="s">
+    <row r="338" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A338" s="10" t="s">
+        <v>5141</v>
+      </c>
+      <c r="B338" s="10" t="s">
+        <v>5134</v>
+      </c>
+      <c r="C338" s="10"/>
+      <c r="D338" s="10"/>
+      <c r="E338" s="10"/>
+      <c r="F338" s="10"/>
+      <c r="G338" s="10"/>
+      <c r="H338" s="10"/>
+      <c r="I338" s="10"/>
+      <c r="J338" s="10"/>
+      <c r="K338" s="10"/>
+      <c r="L338" s="10"/>
+      <c r="M338" s="10"/>
+      <c r="N338" s="10"/>
+      <c r="O338" s="10"/>
+      <c r="P338" s="10"/>
+    </row>
+    <row r="339" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A339" s="3" t="s">
+        <v>5142</v>
+      </c>
+      <c r="B339" s="3" t="s">
+        <v>5143</v>
+      </c>
+      <c r="C339" s="3" t="s">
+        <v>4873</v>
+      </c>
+      <c r="D339" s="3" t="s">
+        <v>4875</v>
+      </c>
+      <c r="E339" s="3" t="s">
+        <v>4874</v>
+      </c>
+      <c r="F339" s="3" t="s">
+        <v>4872</v>
+      </c>
+      <c r="G339" s="3" t="s">
+        <v>4876</v>
+      </c>
+      <c r="H339" s="3" t="s">
+        <v>4877</v>
+      </c>
+      <c r="I339" s="3" t="s">
+        <v>4878</v>
+      </c>
+      <c r="J339" s="3" t="s">
+        <v>4879</v>
+      </c>
+      <c r="K339" s="3" t="s">
+        <v>4880</v>
+      </c>
+      <c r="L339" s="3" t="s">
+        <v>4881</v>
+      </c>
+      <c r="M339" s="3" t="s">
+        <v>4882</v>
+      </c>
+      <c r="N339" s="3" t="s">
+        <v>4883</v>
+      </c>
+      <c r="O339" s="3" t="s">
+        <v>4884</v>
+      </c>
+      <c r="P339" s="3" t="s">
+        <v>4885</v>
+      </c>
+    </row>
+    <row r="340" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="341" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A341" s="3" t="s">
         <v>4946</v>
       </c>
-      <c r="B338" s="3" t="s">
+      <c r="B341" s="3" t="s">
         <v>2415</v>
       </c>
-      <c r="C338" s="3" t="s">
+      <c r="C341" s="3" t="s">
         <v>4950</v>
       </c>
-      <c r="D338" s="3" t="s">
+      <c r="D341" s="3" t="s">
         <v>4951</v>
       </c>
-      <c r="E338" s="3" t="s">
+      <c r="E341" s="3" t="s">
         <v>2415</v>
       </c>
-      <c r="F338" s="3" t="s">
+      <c r="F341" s="3" t="s">
         <v>2543</v>
       </c>
-      <c r="G338" s="3" t="s">
+      <c r="G341" s="3" t="s">
         <v>2437</v>
       </c>
-      <c r="H338" s="3" t="s">
+      <c r="H341" s="3" t="s">
         <v>2448</v>
       </c>
-      <c r="I338" s="3" t="s">
+      <c r="I341" s="3" t="s">
         <v>4952</v>
       </c>
-      <c r="J338" s="3" t="s">
+      <c r="J341" s="3" t="s">
         <v>4953</v>
       </c>
-      <c r="K338" s="3" t="s">
+      <c r="K341" s="3" t="s">
         <v>2459</v>
       </c>
-      <c r="L338" s="3" t="s">
+      <c r="L341" s="3" t="s">
         <v>4954</v>
       </c>
-      <c r="M338" s="3" t="s">
+      <c r="M341" s="3" t="s">
         <v>2437</v>
       </c>
-      <c r="N338" s="3" t="s">
+      <c r="N341" s="3" t="s">
         <v>2479</v>
       </c>
-      <c r="O338" s="3" t="s">
+      <c r="O341" s="3" t="s">
         <v>2491</v>
       </c>
-      <c r="P338" s="3" t="s">
+      <c r="P341" s="3" t="s">
         <v>4949</v>
       </c>
     </row>
-    <row r="339" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A339" s="3" t="s">
+    <row r="342" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A342" s="3" t="s">
         <v>4947</v>
       </c>
-      <c r="B339" s="3" t="s">
+      <c r="B342" s="3" t="s">
         <v>4948</v>
       </c>
-      <c r="C339" s="3" t="s">
+      <c r="C342" s="3" t="s">
         <v>4955</v>
       </c>
-      <c r="D339" s="3" t="s">
+      <c r="D342" s="3" t="s">
         <v>4956</v>
       </c>
-      <c r="E339" s="3" t="s">
+      <c r="E342" s="3" t="s">
         <v>4957</v>
       </c>
-      <c r="F339" s="3" t="s">
+      <c r="F342" s="3" t="s">
         <v>4958</v>
       </c>
-      <c r="G339" s="3" t="s">
+      <c r="G342" s="3" t="s">
         <v>4959</v>
       </c>
-      <c r="H339" s="3" t="s">
+      <c r="H342" s="3" t="s">
         <v>4960</v>
       </c>
-      <c r="I339" s="3" t="s">
+      <c r="I342" s="3" t="s">
         <v>4961</v>
       </c>
-      <c r="J339" s="3" t="s">
+      <c r="J342" s="3" t="s">
         <v>4962</v>
       </c>
-      <c r="K339" s="3" t="s">
+      <c r="K342" s="3" t="s">
         <v>4963</v>
       </c>
-      <c r="L339" s="3" t="s">
+      <c r="L342" s="3" t="s">
         <v>4964</v>
       </c>
-      <c r="M339" s="3" t="s">
+      <c r="M342" s="3" t="s">
         <v>4965</v>
       </c>
-      <c r="N339" s="3" t="s">
+      <c r="N342" s="3" t="s">
         <v>4966</v>
       </c>
-      <c r="O339" s="3" t="s">
+      <c r="O342" s="3" t="s">
         <v>4967</v>
       </c>
-      <c r="P339" s="3" t="s">
+      <c r="P342" s="3" t="s">
         <v>4968</v>
       </c>
     </row>
-    <row r="340" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="341" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A341" s="3" t="s">
+    <row r="343" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="344" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A344" s="3" t="s">
         <v>4870</v>
       </c>
-      <c r="B341" s="3" t="s">
+      <c r="B344" s="3" t="s">
         <v>4871</v>
       </c>
-      <c r="C341" s="3" t="s">
+      <c r="C344" s="3" t="s">
         <v>4873</v>
       </c>
-      <c r="D341" s="3" t="s">
+      <c r="D344" s="3" t="s">
         <v>4875</v>
       </c>
-      <c r="E341" s="3" t="s">
+      <c r="E344" s="3" t="s">
         <v>4874</v>
       </c>
-      <c r="F341" s="3" t="s">
+      <c r="F344" s="3" t="s">
         <v>4872</v>
       </c>
-      <c r="G341" s="3" t="s">
+      <c r="G344" s="3" t="s">
         <v>4876</v>
       </c>
-      <c r="H341" s="3" t="s">
+      <c r="H344" s="3" t="s">
         <v>4877</v>
       </c>
-      <c r="I341" s="3" t="s">
+      <c r="I344" s="3" t="s">
         <v>4878</v>
       </c>
-      <c r="J341" s="3" t="s">
+      <c r="J344" s="3" t="s">
         <v>4879</v>
       </c>
-      <c r="K341" s="3" t="s">
+      <c r="K344" s="3" t="s">
         <v>4880</v>
       </c>
-      <c r="L341" s="3" t="s">
+      <c r="L344" s="3" t="s">
         <v>4881</v>
       </c>
-      <c r="M341" s="3" t="s">
+      <c r="M344" s="3" t="s">
         <v>4882</v>
       </c>
-      <c r="N341" s="3" t="s">
+      <c r="N344" s="3" t="s">
         <v>4883</v>
       </c>
-      <c r="O341" s="3" t="s">
+      <c r="O344" s="3" t="s">
         <v>4884</v>
       </c>
-      <c r="P341" s="3" t="s">
+      <c r="P344" s="3" t="s">
         <v>4885</v>
       </c>
     </row>
-    <row r="342" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A342" s="3" t="s">
+    <row r="345" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A345" s="3" t="s">
         <v>4743</v>
       </c>
-      <c r="B342" s="3" t="s">
+      <c r="B345" s="3" t="s">
         <v>4744</v>
       </c>
-      <c r="C342" s="3" t="s">
+      <c r="C345" s="3" t="s">
         <v>4886</v>
       </c>
-      <c r="D342" s="3" t="s">
+      <c r="D345" s="3" t="s">
         <v>4887</v>
       </c>
-      <c r="E342" s="3" t="s">
+      <c r="E345" s="3" t="s">
         <v>4888</v>
       </c>
-      <c r="F342" s="3" t="s">
+      <c r="F345" s="3" t="s">
         <v>4889</v>
       </c>
-      <c r="G342" s="3" t="s">
+      <c r="G345" s="3" t="s">
         <v>4890</v>
       </c>
-      <c r="H342" s="3" t="s">
+      <c r="H345" s="3" t="s">
         <v>4891</v>
       </c>
-      <c r="I342" s="3" t="s">
+      <c r="I345" s="3" t="s">
         <v>4892</v>
       </c>
-      <c r="J342" s="3" t="s">
+      <c r="J345" s="3" t="s">
         <v>4893</v>
       </c>
-      <c r="K342" s="3" t="s">
+      <c r="K345" s="3" t="s">
         <v>4894</v>
       </c>
-      <c r="L342" s="3" t="s">
+      <c r="L345" s="3" t="s">
         <v>4895</v>
       </c>
-      <c r="M342" s="3" t="s">
+      <c r="M345" s="3" t="s">
         <v>4896</v>
       </c>
-      <c r="N342" s="3" t="s">
+      <c r="N345" s="3" t="s">
         <v>4897</v>
       </c>
-      <c r="O342" s="3" t="s">
+      <c r="O345" s="3" t="s">
         <v>4898</v>
       </c>
-      <c r="P342" s="3" t="s">
+      <c r="P345" s="3" t="s">
         <v>4899</v>
       </c>
     </row>
-    <row r="343" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A343" s="3" t="s">
+    <row r="346" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A346" s="3" t="s">
         <v>4747</v>
       </c>
-      <c r="B343" s="3" t="s">
+      <c r="B346" s="3" t="s">
         <v>4746</v>
       </c>
-      <c r="C343" s="3" t="s">
+      <c r="C346" s="3" t="s">
         <v>4915</v>
       </c>
-      <c r="D343" s="3" t="s">
+      <c r="D346" s="3" t="s">
         <v>4916</v>
       </c>
-      <c r="E343" s="3" t="s">
+      <c r="E346" s="3" t="s">
         <v>4917</v>
       </c>
-      <c r="F343" s="3" t="s">
+      <c r="F346" s="3" t="s">
         <v>4918</v>
       </c>
-      <c r="G343" s="3" t="s">
+      <c r="G346" s="3" t="s">
         <v>4919</v>
       </c>
-      <c r="H343" s="3" t="s">
+      <c r="H346" s="3" t="s">
         <v>4914</v>
       </c>
-      <c r="I343" s="3" t="s">
+      <c r="I346" s="3" t="s">
         <v>4920</v>
       </c>
-      <c r="J343" s="3" t="s">
+      <c r="J346" s="3" t="s">
         <v>4921</v>
       </c>
-      <c r="K343" s="3" t="s">
+      <c r="K346" s="3" t="s">
         <v>4922</v>
       </c>
-      <c r="L343" s="3" t="s">
+      <c r="L346" s="3" t="s">
         <v>4923</v>
       </c>
-      <c r="M343" s="3" t="s">
+      <c r="M346" s="3" t="s">
         <v>4924</v>
       </c>
-      <c r="N343" s="3" t="s">
+      <c r="N346" s="3" t="s">
         <v>4925</v>
       </c>
-      <c r="O343" s="3" t="s">
+      <c r="O346" s="3" t="s">
         <v>4926</v>
       </c>
-      <c r="P343" s="3" t="s">
+      <c r="P346" s="3" t="s">
         <v>4927</v>
       </c>
     </row>
-    <row r="344" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A344" s="3" t="s">
+    <row r="347" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A347" s="3" t="s">
         <v>4748</v>
       </c>
-      <c r="B344" s="3" t="s">
+      <c r="B347" s="3" t="s">
         <v>4745</v>
       </c>
-      <c r="C344" s="3" t="s">
+      <c r="C347" s="3" t="s">
         <v>4900</v>
       </c>
-      <c r="D344" s="3" t="s">
+      <c r="D347" s="3" t="s">
         <v>4901</v>
       </c>
-      <c r="E344" s="3" t="s">
+      <c r="E347" s="3" t="s">
         <v>4902</v>
       </c>
-      <c r="F344" s="3" t="s">
+      <c r="F347" s="3" t="s">
         <v>4903</v>
       </c>
-      <c r="G344" s="3" t="s">
+      <c r="G347" s="3" t="s">
         <v>4904</v>
       </c>
-      <c r="H344" s="3" t="s">
+      <c r="H347" s="3" t="s">
         <v>4905</v>
       </c>
-      <c r="I344" s="3" t="s">
+      <c r="I347" s="3" t="s">
         <v>4906</v>
       </c>
-      <c r="J344" s="3" t="s">
+      <c r="J347" s="3" t="s">
         <v>4907</v>
       </c>
-      <c r="K344" s="3" t="s">
+      <c r="K347" s="3" t="s">
         <v>4908</v>
       </c>
-      <c r="L344" s="3" t="s">
+      <c r="L347" s="3" t="s">
         <v>4909</v>
       </c>
-      <c r="M344" s="3" t="s">
+      <c r="M347" s="3" t="s">
         <v>4910</v>
       </c>
-      <c r="N344" s="3" t="s">
+      <c r="N347" s="3" t="s">
         <v>4911</v>
       </c>
-      <c r="O344" s="3" t="s">
+      <c r="O347" s="3" t="s">
         <v>4912</v>
       </c>
-      <c r="P344" s="3" t="s">
+      <c r="P347" s="3" t="s">
         <v>4913</v>
       </c>
     </row>
-    <row r="345" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A345" s="3" t="s">
+    <row r="348" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A348" s="3" t="s">
         <v>4196</v>
       </c>
-      <c r="B345" s="3" t="s">
+      <c r="B348" s="3" t="s">
         <v>4197</v>
       </c>
-      <c r="C345" s="3" t="s">
+      <c r="C348" s="3" t="s">
         <v>4209</v>
       </c>
-      <c r="D345" s="3" t="s">
+      <c r="D348" s="3" t="s">
         <v>4210</v>
       </c>
-      <c r="E345" s="3" t="s">
+      <c r="E348" s="3" t="s">
         <v>4197</v>
       </c>
-      <c r="F345" s="3" t="s">
+      <c r="F348" s="3" t="s">
         <v>4218</v>
       </c>
-      <c r="G345" s="3" t="s">
+      <c r="G348" s="3" t="s">
         <v>4222</v>
       </c>
-      <c r="H345" s="3" t="s">
+      <c r="H348" s="3" t="s">
         <v>4197</v>
       </c>
-      <c r="I345" s="3" t="s">
+      <c r="I348" s="3" t="s">
         <v>4228</v>
       </c>
-      <c r="J345" s="3" t="s">
+      <c r="J348" s="3" t="s">
         <v>4233</v>
       </c>
-      <c r="K345" s="3" t="s">
+      <c r="K348" s="3" t="s">
         <v>4238</v>
       </c>
-      <c r="L345" s="3" t="s">
+      <c r="L348" s="3" t="s">
         <v>4241</v>
       </c>
-      <c r="M345" s="3" t="s">
+      <c r="M348" s="3" t="s">
         <v>4222</v>
       </c>
-      <c r="N345" s="3" t="s">
+      <c r="N348" s="3" t="s">
         <v>4247</v>
       </c>
-      <c r="O345" s="3" t="s">
+      <c r="O348" s="3" t="s">
         <v>4250</v>
       </c>
-      <c r="P345" s="3" t="s">
+      <c r="P348" s="3" t="s">
         <v>4202</v>
       </c>
     </row>
-    <row r="346" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A346" s="3" t="s">
+    <row r="349" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A349" s="3" t="s">
         <v>4140</v>
       </c>
-      <c r="B346" s="3" t="s">
+      <c r="B349" s="3" t="s">
         <v>4143</v>
       </c>
-      <c r="C346" s="3" t="s">
+      <c r="C349" s="3" t="s">
         <v>4208</v>
       </c>
-      <c r="D346" s="3" t="s">
+      <c r="D349" s="3" t="s">
         <v>4211</v>
       </c>
-      <c r="E346" s="3" t="s">
+      <c r="E349" s="3" t="s">
         <v>4216</v>
       </c>
-      <c r="F346" s="3" t="s">
+      <c r="F349" s="3" t="s">
         <v>4217</v>
       </c>
-      <c r="G346" s="3" t="s">
+      <c r="G349" s="3" t="s">
         <v>4223</v>
       </c>
-      <c r="H346" s="3" t="s">
+      <c r="H349" s="3" t="s">
         <v>4226</v>
       </c>
-      <c r="I346" s="3" t="s">
+      <c r="I349" s="3" t="s">
         <v>4229</v>
       </c>
-      <c r="J346" s="3" t="s">
+      <c r="J349" s="3" t="s">
         <v>4234</v>
       </c>
-      <c r="K346" s="3" t="s">
+      <c r="K349" s="3" t="s">
         <v>4239</v>
       </c>
-      <c r="L346" s="3" t="s">
+      <c r="L349" s="3" t="s">
         <v>4240</v>
       </c>
-      <c r="M346" s="3" t="s">
+      <c r="M349" s="3" t="s">
         <v>4223</v>
       </c>
-      <c r="N346" s="3" t="s">
+      <c r="N349" s="3" t="s">
         <v>4248</v>
       </c>
-      <c r="O346" s="3" t="s">
+      <c r="O349" s="3" t="s">
         <v>4249</v>
       </c>
-      <c r="P346" s="3" t="s">
+      <c r="P349" s="3" t="s">
         <v>4203</v>
       </c>
     </row>
-    <row r="347" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A347" s="3" t="s">
+    <row r="350" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A350" s="3" t="s">
         <v>4141</v>
       </c>
-      <c r="B347" s="3" t="s">
+      <c r="B350" s="3" t="s">
         <v>4144</v>
       </c>
-      <c r="C347" s="3" t="s">
+      <c r="C350" s="3" t="s">
         <v>4207</v>
       </c>
-      <c r="D347" s="3" t="s">
+      <c r="D350" s="3" t="s">
         <v>4212</v>
       </c>
-      <c r="E347" s="3" t="s">
+      <c r="E350" s="3" t="s">
         <v>4215</v>
       </c>
-      <c r="F347" s="3" t="s">
+      <c r="F350" s="3" t="s">
         <v>4219</v>
       </c>
-      <c r="G347" s="3" t="s">
+      <c r="G350" s="3" t="s">
         <v>4224</v>
       </c>
-      <c r="H347" s="3" t="s">
+      <c r="H350" s="3" t="s">
         <v>4225</v>
       </c>
-      <c r="I347" s="3" t="s">
+      <c r="I350" s="3" t="s">
         <v>4230</v>
       </c>
-      <c r="J347" s="3" t="s">
+      <c r="J350" s="3" t="s">
         <v>4235</v>
       </c>
-      <c r="K347" s="3" t="s">
+      <c r="K350" s="3" t="s">
         <v>4236</v>
       </c>
-      <c r="L347" s="3" t="s">
+      <c r="L350" s="3" t="s">
         <v>4242</v>
       </c>
-      <c r="M347" s="3" t="s">
+      <c r="M350" s="3" t="s">
         <v>4244</v>
       </c>
-      <c r="N347" s="3" t="s">
+      <c r="N350" s="3" t="s">
         <v>4245</v>
       </c>
-      <c r="O347" s="3" t="s">
+      <c r="O350" s="3" t="s">
         <v>4251</v>
       </c>
-      <c r="P347" s="3" t="s">
+      <c r="P350" s="3" t="s">
         <v>4204</v>
       </c>
     </row>
-    <row r="348" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A348" s="3" t="s">
+    <row r="351" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A351" s="3" t="s">
         <v>4142</v>
       </c>
-      <c r="B348" s="3" t="s">
+      <c r="B351" s="3" t="s">
         <v>4145</v>
       </c>
-      <c r="C348" s="3" t="s">
+      <c r="C351" s="3" t="s">
         <v>4206</v>
       </c>
-      <c r="D348" s="3" t="s">
+      <c r="D351" s="3" t="s">
         <v>4213</v>
       </c>
-      <c r="E348" s="3" t="s">
+      <c r="E351" s="3" t="s">
         <v>4214</v>
       </c>
-      <c r="F348" s="3" t="s">
+      <c r="F351" s="3" t="s">
         <v>4220</v>
       </c>
-      <c r="G348" s="3" t="s">
+      <c r="G351" s="3" t="s">
         <v>4221</v>
       </c>
-      <c r="H348" s="3" t="s">
+      <c r="H351" s="3" t="s">
         <v>4227</v>
       </c>
-      <c r="I348" s="3" t="s">
+      <c r="I351" s="3" t="s">
         <v>4231</v>
       </c>
-      <c r="J348" s="3" t="s">
+      <c r="J351" s="3" t="s">
         <v>4232</v>
       </c>
-      <c r="K348" s="3" t="s">
+      <c r="K351" s="3" t="s">
         <v>4237</v>
       </c>
-      <c r="L348" s="3" t="s">
+      <c r="L351" s="3" t="s">
         <v>4243</v>
       </c>
-      <c r="M348" s="3" t="s">
+      <c r="M351" s="3" t="s">
         <v>4221</v>
       </c>
-      <c r="N348" s="3" t="s">
+      <c r="N351" s="3" t="s">
         <v>4246</v>
       </c>
-      <c r="O348" s="3" t="s">
+      <c r="O351" s="3" t="s">
         <v>4252</v>
       </c>
-      <c r="P348" s="3" t="s">
+      <c r="P351" s="3" t="s">
         <v>4205</v>
       </c>
     </row>
-    <row r="349" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A349" s="3" t="s">
+    <row r="352" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A352" s="3" t="s">
         <v>4146</v>
       </c>
-      <c r="B349" s="3" t="s">
+      <c r="B352" s="3" t="s">
         <v>4149</v>
       </c>
-      <c r="C349" s="3" t="s">
+      <c r="C352" s="3" t="s">
         <v>4352</v>
       </c>
-      <c r="D349" s="3" t="s">
+      <c r="D352" s="3" t="s">
         <v>4351</v>
       </c>
-      <c r="E349" s="3" t="s">
+      <c r="E352" s="3" t="s">
         <v>4353</v>
       </c>
-      <c r="F349" s="3" t="s">
+      <c r="F352" s="3" t="s">
         <v>4354</v>
       </c>
-      <c r="G349" s="3" t="s">
+      <c r="G352" s="3" t="s">
         <v>4355</v>
       </c>
-      <c r="H349" s="3" t="s">
+      <c r="H352" s="3" t="s">
         <v>4356</v>
       </c>
-      <c r="I349" s="3" t="s">
+      <c r="I352" s="3" t="s">
         <v>4357</v>
       </c>
-      <c r="J349" s="3" t="s">
+      <c r="J352" s="3" t="s">
         <v>4358</v>
       </c>
-      <c r="K349" s="3" t="s">
+      <c r="K352" s="3" t="s">
         <v>4359</v>
       </c>
-      <c r="L349" s="3" t="s">
+      <c r="L352" s="3" t="s">
         <v>4360</v>
       </c>
-      <c r="M349" s="3" t="s">
+      <c r="M352" s="3" t="s">
         <v>4361</v>
       </c>
-      <c r="N349" s="3" t="s">
+      <c r="N352" s="3" t="s">
         <v>4362</v>
       </c>
-      <c r="O349" s="3" t="s">
+      <c r="O352" s="3" t="s">
         <v>4363</v>
       </c>
-      <c r="P349" s="3" t="s">
+      <c r="P352" s="3" t="s">
         <v>4364</v>
       </c>
     </row>
-    <row r="350" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A350" s="3" t="s">
+    <row r="353" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A353" s="3" t="s">
         <v>4147</v>
       </c>
-      <c r="B350" s="3" t="s">
+      <c r="B353" s="3" t="s">
         <v>4150</v>
       </c>
-      <c r="C350" s="3" t="s">
+      <c r="C353" s="3" t="s">
         <v>4367</v>
       </c>
-      <c r="D350" s="3" t="s">
+      <c r="D353" s="3" t="s">
         <v>4368</v>
       </c>
-      <c r="E350" s="3" t="s">
+      <c r="E353" s="3" t="s">
         <v>4365</v>
       </c>
-      <c r="F350" s="3" t="s">
+      <c r="F353" s="3" t="s">
         <v>4366</v>
       </c>
-      <c r="G350" s="3" t="s">
+      <c r="G353" s="3" t="s">
         <v>4369</v>
       </c>
-      <c r="H350" s="3" t="s">
+      <c r="H353" s="3" t="s">
         <v>4370</v>
       </c>
-      <c r="I350" s="3" t="s">
+      <c r="I353" s="3" t="s">
         <v>4371</v>
       </c>
-      <c r="J350" s="3" t="s">
+      <c r="J353" s="3" t="s">
         <v>4372</v>
       </c>
-      <c r="K350" s="3" t="s">
+      <c r="K353" s="3" t="s">
         <v>4373</v>
       </c>
-      <c r="L350" s="3" t="s">
+      <c r="L353" s="3" t="s">
         <v>4374</v>
       </c>
-      <c r="M350" s="3" t="s">
+      <c r="M353" s="3" t="s">
         <v>4375</v>
       </c>
-      <c r="N350" s="3" t="s">
+      <c r="N353" s="3" t="s">
         <v>4376</v>
       </c>
-      <c r="O350" s="3" t="s">
+      <c r="O353" s="3" t="s">
         <v>4377</v>
       </c>
-      <c r="P350" s="3" t="s">
+      <c r="P353" s="3" t="s">
         <v>4378</v>
       </c>
     </row>
-    <row r="351" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A351" s="3" t="s">
+    <row r="354" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A354" s="3" t="s">
         <v>4148</v>
       </c>
-      <c r="B351" s="3" t="s">
+      <c r="B354" s="3" t="s">
         <v>4151</v>
       </c>
-      <c r="C351" s="3" t="s">
+      <c r="C354" s="3" t="s">
         <v>4379</v>
       </c>
-      <c r="D351" s="3" t="s">
+      <c r="D354" s="3" t="s">
         <v>4380</v>
       </c>
-      <c r="E351" s="3" t="s">
+      <c r="E354" s="3" t="s">
         <v>4381</v>
       </c>
-      <c r="F351" s="3" t="s">
+      <c r="F354" s="3" t="s">
         <v>4382</v>
       </c>
-      <c r="G351" s="3" t="s">
+      <c r="G354" s="3" t="s">
         <v>4384</v>
       </c>
-      <c r="H351" s="3" t="s">
+      <c r="H354" s="3" t="s">
         <v>4383</v>
       </c>
-      <c r="I351" s="3" t="s">
+      <c r="I354" s="3" t="s">
         <v>4385</v>
       </c>
-      <c r="J351" s="3" t="s">
+      <c r="J354" s="3" t="s">
         <v>4386</v>
       </c>
-      <c r="K351" s="3" t="s">
+      <c r="K354" s="3" t="s">
         <v>4387</v>
       </c>
-      <c r="L351" s="3" t="s">
+      <c r="L354" s="3" t="s">
         <v>4388</v>
       </c>
-      <c r="M351" s="3" t="s">
+      <c r="M354" s="3" t="s">
         <v>4384</v>
       </c>
-      <c r="N351" s="3" t="s">
+      <c r="N354" s="3" t="s">
         <v>4389</v>
-      </c>
-      <c r="O351" s="3" t="s">
-        <v>886</v>
-      </c>
-      <c r="P351" s="3" t="s">
-        <v>2250</v>
-      </c>
-    </row>
-    <row r="352" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A352" s="3" t="s">
-        <v>4152</v>
-      </c>
-      <c r="B352" s="3" t="s">
-        <v>4173</v>
-      </c>
-      <c r="C352" s="3" t="s">
-        <v>4411</v>
-      </c>
-      <c r="D352" s="3" t="s">
-        <v>4410</v>
-      </c>
-      <c r="E352" s="3" t="s">
-        <v>4407</v>
-      </c>
-      <c r="F352" s="3" t="s">
-        <v>4406</v>
-      </c>
-      <c r="G352" s="3" t="s">
-        <v>4396</v>
-      </c>
-      <c r="H352" s="3" t="s">
-        <v>4416</v>
-      </c>
-      <c r="I352" s="3" t="s">
-        <v>4403</v>
-      </c>
-      <c r="J352" s="3" t="s">
-        <v>4400</v>
-      </c>
-      <c r="K352" s="3" t="s">
-        <v>4396</v>
-      </c>
-      <c r="L352" s="3" t="s">
-        <v>4397</v>
-      </c>
-      <c r="M352" s="3" t="s">
-        <v>4396</v>
-      </c>
-      <c r="N352" s="3" t="s">
-        <v>4393</v>
-      </c>
-      <c r="O352" s="3" t="s">
-        <v>3616</v>
-      </c>
-      <c r="P352" s="3" t="s">
-        <v>4390</v>
-      </c>
-    </row>
-    <row r="353" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A353" s="3" t="s">
-        <v>4153</v>
-      </c>
-      <c r="B353" s="3" t="s">
-        <v>4174</v>
-      </c>
-      <c r="C353" s="3" t="s">
-        <v>4412</v>
-      </c>
-      <c r="D353" s="3" t="s">
-        <v>4409</v>
-      </c>
-      <c r="E353" s="3" t="s">
-        <v>4408</v>
-      </c>
-      <c r="F353" s="3" t="s">
-        <v>4405</v>
-      </c>
-      <c r="G353" s="3" t="s">
-        <v>4404</v>
-      </c>
-      <c r="H353" s="3" t="s">
-        <v>4417</v>
-      </c>
-      <c r="I353" s="3" t="s">
-        <v>4402</v>
-      </c>
-      <c r="J353" s="3" t="s">
-        <v>4401</v>
-      </c>
-      <c r="K353" s="3" t="s">
-        <v>4399</v>
-      </c>
-      <c r="L353" s="3" t="s">
-        <v>4398</v>
-      </c>
-      <c r="M353" s="3" t="s">
-        <v>4395</v>
-      </c>
-      <c r="N353" s="3" t="s">
-        <v>4394</v>
-      </c>
-      <c r="O353" s="3" t="s">
-        <v>4392</v>
-      </c>
-      <c r="P353" s="3" t="s">
-        <v>4391</v>
-      </c>
-    </row>
-    <row r="354" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A354" s="3" t="s">
-        <v>4154</v>
-      </c>
-      <c r="B354" s="3" t="s">
-        <v>4175</v>
-      </c>
-      <c r="C354" s="3" t="s">
-        <v>1462</v>
-      </c>
-      <c r="D354" s="3" t="s">
-        <v>4413</v>
-      </c>
-      <c r="E354" s="3" t="s">
-        <v>2600</v>
-      </c>
-      <c r="F354" s="3" t="s">
-        <v>2641</v>
-      </c>
-      <c r="G354" s="3" t="s">
-        <v>4415</v>
-      </c>
-      <c r="H354" s="3" t="s">
-        <v>4414</v>
-      </c>
-      <c r="I354" s="3" t="s">
-        <v>4420</v>
-      </c>
-      <c r="J354" s="3" t="s">
-        <v>4418</v>
-      </c>
-      <c r="K354" s="3" t="s">
-        <v>4419</v>
-      </c>
-      <c r="L354" s="3" t="s">
-        <v>4421</v>
-      </c>
-      <c r="M354" s="3" t="s">
-        <v>4422</v>
-      </c>
-      <c r="N354" s="3" t="s">
-        <v>4423</v>
       </c>
       <c r="O354" s="3" t="s">
         <v>886</v>
       </c>
       <c r="P354" s="3" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="355" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A355" s="3" t="s">
+        <v>4152</v>
+      </c>
+      <c r="B355" s="3" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C355" s="3" t="s">
+        <v>4411</v>
+      </c>
+      <c r="D355" s="3" t="s">
+        <v>4410</v>
+      </c>
+      <c r="E355" s="3" t="s">
+        <v>4407</v>
+      </c>
+      <c r="F355" s="3" t="s">
+        <v>4406</v>
+      </c>
+      <c r="G355" s="3" t="s">
+        <v>4396</v>
+      </c>
+      <c r="H355" s="3" t="s">
+        <v>4416</v>
+      </c>
+      <c r="I355" s="3" t="s">
+        <v>4403</v>
+      </c>
+      <c r="J355" s="3" t="s">
+        <v>4400</v>
+      </c>
+      <c r="K355" s="3" t="s">
+        <v>4396</v>
+      </c>
+      <c r="L355" s="3" t="s">
+        <v>4397</v>
+      </c>
+      <c r="M355" s="3" t="s">
+        <v>4396</v>
+      </c>
+      <c r="N355" s="3" t="s">
+        <v>4393</v>
+      </c>
+      <c r="O355" s="3" t="s">
+        <v>3616</v>
+      </c>
+      <c r="P355" s="3" t="s">
+        <v>4390</v>
+      </c>
+    </row>
+    <row r="356" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A356" s="3" t="s">
+        <v>4153</v>
+      </c>
+      <c r="B356" s="3" t="s">
+        <v>4174</v>
+      </c>
+      <c r="C356" s="3" t="s">
+        <v>4412</v>
+      </c>
+      <c r="D356" s="3" t="s">
+        <v>4409</v>
+      </c>
+      <c r="E356" s="3" t="s">
+        <v>4408</v>
+      </c>
+      <c r="F356" s="3" t="s">
+        <v>4405</v>
+      </c>
+      <c r="G356" s="3" t="s">
+        <v>4404</v>
+      </c>
+      <c r="H356" s="3" t="s">
+        <v>4417</v>
+      </c>
+      <c r="I356" s="3" t="s">
+        <v>4402</v>
+      </c>
+      <c r="J356" s="3" t="s">
+        <v>4401</v>
+      </c>
+      <c r="K356" s="3" t="s">
+        <v>4399</v>
+      </c>
+      <c r="L356" s="3" t="s">
+        <v>4398</v>
+      </c>
+      <c r="M356" s="3" t="s">
+        <v>4395</v>
+      </c>
+      <c r="N356" s="3" t="s">
+        <v>4394</v>
+      </c>
+      <c r="O356" s="3" t="s">
+        <v>4392</v>
+      </c>
+      <c r="P356" s="3" t="s">
+        <v>4391</v>
+      </c>
+    </row>
+    <row r="357" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A357" s="3" t="s">
+        <v>4154</v>
+      </c>
+      <c r="B357" s="3" t="s">
+        <v>4175</v>
+      </c>
+      <c r="C357" s="3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D357" s="3" t="s">
+        <v>4413</v>
+      </c>
+      <c r="E357" s="3" t="s">
+        <v>2600</v>
+      </c>
+      <c r="F357" s="3" t="s">
+        <v>2641</v>
+      </c>
+      <c r="G357" s="3" t="s">
+        <v>4415</v>
+      </c>
+      <c r="H357" s="3" t="s">
+        <v>4414</v>
+      </c>
+      <c r="I357" s="3" t="s">
+        <v>4420</v>
+      </c>
+      <c r="J357" s="3" t="s">
+        <v>4418</v>
+      </c>
+      <c r="K357" s="3" t="s">
+        <v>4419</v>
+      </c>
+      <c r="L357" s="3" t="s">
+        <v>4421</v>
+      </c>
+      <c r="M357" s="3" t="s">
+        <v>4422</v>
+      </c>
+      <c r="N357" s="3" t="s">
+        <v>4423</v>
+      </c>
+      <c r="O357" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="P357" s="3" t="s">
         <v>4424</v>
       </c>
     </row>
-    <row r="355" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="3" t="s">
+    <row r="358" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A358" s="3" t="s">
         <v>4155</v>
       </c>
-      <c r="B355" s="3" t="s">
+      <c r="B358" s="3" t="s">
         <v>4176</v>
       </c>
-      <c r="C355" s="3" t="s">
+      <c r="C358" s="3" t="s">
         <v>4431</v>
       </c>
-      <c r="D355" s="3" t="s">
+      <c r="D358" s="3" t="s">
         <v>4434</v>
       </c>
-      <c r="E355" s="3" t="s">
+      <c r="E358" s="3" t="s">
         <v>4435</v>
       </c>
-      <c r="F355" s="3" t="s">
+      <c r="F358" s="3" t="s">
         <v>4438</v>
       </c>
-      <c r="G355" s="3" t="s">
+      <c r="G358" s="3" t="s">
         <v>4522</v>
       </c>
-      <c r="H355" s="3" t="s">
+      <c r="H358" s="3" t="s">
         <v>4523</v>
       </c>
-      <c r="I355" s="3" t="s">
+      <c r="I358" s="3" t="s">
         <v>4439</v>
       </c>
-      <c r="J355" s="3" t="s">
+      <c r="J358" s="3" t="s">
         <v>4444</v>
       </c>
-      <c r="K355" s="3" t="s">
+      <c r="K358" s="3" t="s">
         <v>4522</v>
       </c>
-      <c r="L355" s="3" t="s">
+      <c r="L358" s="3" t="s">
         <v>4443</v>
       </c>
-      <c r="M355" s="3" t="s">
+      <c r="M358" s="3" t="s">
         <v>4522</v>
       </c>
-      <c r="N355" s="3" t="s">
+      <c r="N358" s="3" t="s">
         <v>4445</v>
       </c>
-      <c r="O355" s="3" t="s">
+      <c r="O358" s="3" t="s">
         <v>4554</v>
       </c>
-      <c r="P355" s="3" t="s">
+      <c r="P358" s="3" t="s">
         <v>4446</v>
       </c>
     </row>
-    <row r="356" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="3" t="s">
+    <row r="359" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A359" s="3" t="s">
         <v>4156</v>
       </c>
-      <c r="B356" s="3" t="s">
+      <c r="B359" s="3" t="s">
         <v>4182</v>
       </c>
-      <c r="C356" s="3" t="s">
+      <c r="C359" s="3" t="s">
         <v>4432</v>
       </c>
-      <c r="D356" s="3" t="s">
+      <c r="D359" s="3" t="s">
         <v>4433</v>
       </c>
-      <c r="E356" s="3" t="s">
+      <c r="E359" s="3" t="s">
         <v>4436</v>
       </c>
-      <c r="F356" s="3" t="s">
+      <c r="F359" s="3" t="s">
         <v>4437</v>
       </c>
-      <c r="G356" s="3" t="s">
+      <c r="G359" s="3" t="s">
         <v>4521</v>
       </c>
-      <c r="H356" s="3" t="s">
+      <c r="H359" s="3" t="s">
         <v>4524</v>
       </c>
-      <c r="I356" s="3" t="s">
+      <c r="I359" s="3" t="s">
         <v>4440</v>
       </c>
-      <c r="J356" s="3" t="s">
+      <c r="J359" s="3" t="s">
         <v>4441</v>
       </c>
-      <c r="K356" s="3" t="s">
+      <c r="K359" s="3" t="s">
         <v>4532</v>
       </c>
-      <c r="L356" s="3" t="s">
+      <c r="L359" s="3" t="s">
         <v>4442</v>
       </c>
-      <c r="M356" s="3" t="s">
+      <c r="M359" s="3" t="s">
         <v>4521</v>
       </c>
-      <c r="N356" s="3" t="s">
+      <c r="N359" s="3" t="s">
         <v>4448</v>
       </c>
-      <c r="O356" s="3" t="s">
+      <c r="O359" s="3" t="s">
         <v>4555</v>
       </c>
-      <c r="P356" s="3" t="s">
+      <c r="P359" s="3" t="s">
         <v>4447</v>
       </c>
     </row>
-    <row r="357" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A357" s="3" t="s">
+    <row r="360" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A360" s="3" t="s">
         <v>4157</v>
       </c>
-      <c r="B357" s="3" t="s">
+      <c r="B360" s="3" t="s">
         <v>4184</v>
       </c>
-      <c r="C357" s="3" t="s">
+      <c r="C360" s="3" t="s">
         <v>4449</v>
       </c>
-      <c r="D357" s="3" t="s">
+      <c r="D360" s="3" t="s">
         <v>4450</v>
       </c>
-      <c r="E357" s="3" t="s">
+      <c r="E360" s="3" t="s">
         <v>4451</v>
       </c>
-      <c r="F357" s="3" t="s">
+      <c r="F360" s="3" t="s">
         <v>4452</v>
       </c>
-      <c r="G357" s="3" t="s">
+      <c r="G360" s="3" t="s">
         <v>4520</v>
       </c>
-      <c r="H357" s="3" t="s">
+      <c r="H360" s="3" t="s">
         <v>4525</v>
       </c>
-      <c r="I357" s="3" t="s">
+      <c r="I360" s="3" t="s">
         <v>4453</v>
       </c>
-      <c r="J357" s="3" t="s">
+      <c r="J360" s="3" t="s">
         <v>4454</v>
       </c>
-      <c r="K357" s="3" t="s">
+      <c r="K360" s="3" t="s">
         <v>4533</v>
       </c>
-      <c r="L357" s="3" t="s">
+      <c r="L360" s="3" t="s">
         <v>4455</v>
       </c>
-      <c r="M357" s="3" t="s">
+      <c r="M360" s="3" t="s">
         <v>4540</v>
       </c>
-      <c r="N357" s="3" t="s">
+      <c r="N360" s="3" t="s">
         <v>4456</v>
       </c>
-      <c r="O357" s="3" t="s">
+      <c r="O360" s="3" t="s">
         <v>4556</v>
       </c>
-      <c r="P357" s="3" t="s">
+      <c r="P360" s="3" t="s">
         <v>4457</v>
       </c>
     </row>
-    <row r="358" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A358" s="3" t="s">
+    <row r="361" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A361" s="3" t="s">
         <v>4158</v>
       </c>
-      <c r="B358" s="3" t="s">
+      <c r="B361" s="3" t="s">
         <v>4183</v>
       </c>
-      <c r="C358" s="3" t="s">
+      <c r="C361" s="3" t="s">
         <v>4458</v>
       </c>
-      <c r="D358" s="3" t="s">
+      <c r="D361" s="3" t="s">
         <v>4459</v>
       </c>
-      <c r="E358" s="3" t="s">
+      <c r="E361" s="3" t="s">
         <v>4460</v>
       </c>
-      <c r="F358" s="3" t="s">
+      <c r="F361" s="3" t="s">
         <v>4461</v>
       </c>
-      <c r="G358" s="3" t="s">
+      <c r="G361" s="3" t="s">
         <v>4519</v>
       </c>
-      <c r="H358" s="3" t="s">
+      <c r="H361" s="3" t="s">
         <v>4526</v>
       </c>
-      <c r="I358" s="3" t="s">
+      <c r="I361" s="3" t="s">
         <v>4462</v>
       </c>
-      <c r="J358" s="3" t="s">
+      <c r="J361" s="3" t="s">
         <v>4463</v>
       </c>
-      <c r="K358" s="3" t="s">
+      <c r="K361" s="3" t="s">
         <v>4534</v>
       </c>
-      <c r="L358" s="3" t="s">
+      <c r="L361" s="3" t="s">
         <v>4464</v>
       </c>
-      <c r="M358" s="3" t="s">
+      <c r="M361" s="3" t="s">
         <v>4541</v>
       </c>
-      <c r="N358" s="3" t="s">
+      <c r="N361" s="3" t="s">
         <v>4465</v>
       </c>
-      <c r="O358" s="3" t="s">
+      <c r="O361" s="3" t="s">
         <v>4557</v>
       </c>
-      <c r="P358" s="3" t="s">
+      <c r="P361" s="3" t="s">
         <v>4466</v>
       </c>
     </row>
-    <row r="359" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A359" s="3" t="s">
+    <row r="362" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A362" s="3" t="s">
         <v>4159</v>
       </c>
-      <c r="B359" s="3" t="s">
+      <c r="B362" s="3" t="s">
         <v>4185</v>
       </c>
-      <c r="C359" s="3" t="s">
+      <c r="C362" s="3" t="s">
         <v>4467</v>
       </c>
-      <c r="D359" s="3" t="s">
+      <c r="D362" s="3" t="s">
         <v>4468</v>
       </c>
-      <c r="E359" s="3" t="s">
+      <c r="E362" s="3" t="s">
         <v>4469</v>
       </c>
-      <c r="F359" s="3" t="s">
+      <c r="F362" s="3" t="s">
         <v>4470</v>
       </c>
-      <c r="G359" s="3" t="s">
+      <c r="G362" s="3" t="s">
         <v>4518</v>
       </c>
-      <c r="H359" s="3" t="s">
+      <c r="H362" s="3" t="s">
         <v>4527</v>
       </c>
-      <c r="I359" s="3" t="s">
+      <c r="I362" s="3" t="s">
         <v>4471</v>
       </c>
-      <c r="J359" s="3" t="s">
+      <c r="J362" s="3" t="s">
         <v>4472</v>
       </c>
-      <c r="K359" s="3" t="s">
+      <c r="K362" s="3" t="s">
         <v>4535</v>
       </c>
-      <c r="L359" s="3" t="s">
+      <c r="L362" s="3" t="s">
         <v>4473</v>
       </c>
-      <c r="M359" s="3" t="s">
+      <c r="M362" s="3" t="s">
         <v>4542</v>
       </c>
-      <c r="N359" s="3" t="s">
+      <c r="N362" s="3" t="s">
         <v>4474</v>
       </c>
-      <c r="O359" s="3" t="s">
+      <c r="O362" s="3" t="s">
         <v>4604</v>
       </c>
-      <c r="P359" s="3" t="s">
+      <c r="P362" s="3" t="s">
         <v>4475</v>
       </c>
     </row>
-    <row r="360" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A360" s="3" t="s">
+    <row r="363" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A363" s="3" t="s">
         <v>4187</v>
       </c>
-      <c r="B360" s="3" t="s">
+      <c r="B363" s="3" t="s">
         <v>4186</v>
       </c>
-      <c r="C360" s="3" t="s">
+      <c r="C363" s="3" t="s">
         <v>4476</v>
       </c>
-      <c r="D360" s="3" t="s">
+      <c r="D363" s="3" t="s">
         <v>4477</v>
       </c>
-      <c r="E360" s="3" t="s">
+      <c r="E363" s="3" t="s">
         <v>4478</v>
       </c>
-      <c r="F360" s="3" t="s">
+      <c r="F363" s="3" t="s">
         <v>4479</v>
       </c>
-      <c r="G360" s="3" t="s">
+      <c r="G363" s="3" t="s">
         <v>4517</v>
       </c>
-      <c r="H360" s="3" t="s">
+      <c r="H363" s="3" t="s">
         <v>4528</v>
       </c>
-      <c r="I360" s="3" t="s">
+      <c r="I363" s="3" t="s">
         <v>4480</v>
       </c>
-      <c r="J360" s="3" t="s">
+      <c r="J363" s="3" t="s">
         <v>4481</v>
       </c>
-      <c r="K360" s="3" t="s">
+      <c r="K363" s="3" t="s">
         <v>4536</v>
       </c>
-      <c r="L360" s="3" t="s">
+      <c r="L363" s="3" t="s">
         <v>4482</v>
       </c>
-      <c r="M360" s="3" t="s">
+      <c r="M363" s="3" t="s">
         <v>4543</v>
       </c>
-      <c r="N360" s="3" t="s">
+      <c r="N363" s="3" t="s">
         <v>4483</v>
       </c>
-      <c r="O360" s="3" t="s">
+      <c r="O363" s="3" t="s">
         <v>4558</v>
       </c>
-      <c r="P360" s="3" t="s">
+      <c r="P363" s="3" t="s">
         <v>4484</v>
       </c>
     </row>
-    <row r="361" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A361" s="3" t="s">
+    <row r="364" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A364" s="3" t="s">
         <v>4160</v>
       </c>
-      <c r="B361" s="3" t="s">
+      <c r="B364" s="3" t="s">
         <v>4188</v>
       </c>
-      <c r="C361" s="3" t="s">
+      <c r="C364" s="3" t="s">
         <v>4485</v>
       </c>
-      <c r="D361" s="3" t="s">
+      <c r="D364" s="3" t="s">
         <v>4486</v>
       </c>
-      <c r="E361" s="3" t="s">
+      <c r="E364" s="3" t="s">
         <v>4487</v>
       </c>
-      <c r="F361" s="3" t="s">
+      <c r="F364" s="3" t="s">
         <v>4488</v>
       </c>
-      <c r="G361" s="3" t="s">
+      <c r="G364" s="3" t="s">
         <v>4516</v>
       </c>
-      <c r="H361" s="3" t="s">
+      <c r="H364" s="3" t="s">
         <v>4529</v>
       </c>
-      <c r="I361" s="3" t="s">
+      <c r="I364" s="3" t="s">
         <v>4489</v>
       </c>
-      <c r="J361" s="3" t="s">
+      <c r="J364" s="3" t="s">
         <v>2135</v>
       </c>
-      <c r="K361" s="3" t="s">
+      <c r="K364" s="3" t="s">
         <v>4537</v>
       </c>
-      <c r="L361" s="3" t="s">
+      <c r="L364" s="3" t="s">
         <v>4490</v>
       </c>
-      <c r="M361" s="3" t="s">
+      <c r="M364" s="3" t="s">
         <v>4516</v>
       </c>
-      <c r="N361" s="3" t="s">
+      <c r="N364" s="3" t="s">
         <v>4491</v>
       </c>
-      <c r="O361" s="3" t="s">
+      <c r="O364" s="3" t="s">
         <v>4559</v>
       </c>
-      <c r="P361" s="3" t="s">
+      <c r="P364" s="3" t="s">
         <v>2118</v>
       </c>
     </row>
-    <row r="362" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A362" s="3" t="s">
+    <row r="365" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A365" s="3" t="s">
         <v>4161</v>
       </c>
-      <c r="B362" s="3" t="s">
+      <c r="B365" s="3" t="s">
         <v>4189</v>
       </c>
-      <c r="C362" s="3" t="s">
+      <c r="C365" s="3" t="s">
         <v>4492</v>
       </c>
-      <c r="D362" s="3" t="s">
+      <c r="D365" s="3" t="s">
         <v>4493</v>
       </c>
-      <c r="E362" s="3" t="s">
+      <c r="E365" s="3" t="s">
         <v>4494</v>
       </c>
-      <c r="F362" s="3" t="s">
+      <c r="F365" s="3" t="s">
         <v>4495</v>
       </c>
-      <c r="G362" s="3" t="s">
+      <c r="G365" s="3" t="s">
         <v>4515</v>
       </c>
-      <c r="H362" s="3" t="s">
+      <c r="H365" s="3" t="s">
         <v>4530</v>
       </c>
-      <c r="I362" s="3" t="s">
+      <c r="I365" s="3" t="s">
         <v>4496</v>
       </c>
-      <c r="J362" s="3" t="s">
+      <c r="J365" s="3" t="s">
         <v>4497</v>
       </c>
-      <c r="K362" s="3" t="s">
+      <c r="K365" s="3" t="s">
         <v>4538</v>
       </c>
-      <c r="L362" s="3" t="s">
+      <c r="L365" s="3" t="s">
         <v>824</v>
       </c>
-      <c r="M362" s="3" t="s">
+      <c r="M365" s="3" t="s">
         <v>4544</v>
       </c>
-      <c r="N362" s="3" t="s">
+      <c r="N365" s="3" t="s">
         <v>4498</v>
       </c>
-      <c r="O362" s="3" t="s">
+      <c r="O365" s="3" t="s">
         <v>4560</v>
       </c>
-      <c r="P362" s="3" t="s">
+      <c r="P365" s="3" t="s">
         <v>4499</v>
       </c>
     </row>
-    <row r="363" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A363" s="3" t="s">
+    <row r="366" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A366" s="3" t="s">
         <v>4162</v>
       </c>
-      <c r="B363" s="3" t="s">
+      <c r="B366" s="3" t="s">
         <v>4190</v>
       </c>
-      <c r="C363" s="3" t="s">
+      <c r="C366" s="3" t="s">
         <v>4501</v>
       </c>
-      <c r="D363" s="3" t="s">
+      <c r="D366" s="3" t="s">
         <v>4502</v>
       </c>
-      <c r="E363" s="3" t="s">
+      <c r="E366" s="3" t="s">
         <v>4503</v>
       </c>
-      <c r="F363" s="3" t="s">
+      <c r="F366" s="3" t="s">
         <v>4504</v>
       </c>
-      <c r="G363" s="3" t="s">
+      <c r="G366" s="3" t="s">
         <v>4514</v>
       </c>
-      <c r="H363" s="3" t="s">
+      <c r="H366" s="3" t="s">
         <v>4531</v>
       </c>
-      <c r="I363" s="3" t="s">
+      <c r="I366" s="3" t="s">
         <v>4505</v>
       </c>
-      <c r="J363" s="3" t="s">
+      <c r="J366" s="3" t="s">
         <v>4506</v>
       </c>
-      <c r="K363" s="3" t="s">
+      <c r="K366" s="3" t="s">
         <v>4539</v>
       </c>
-      <c r="L363" s="3" t="s">
+      <c r="L366" s="3" t="s">
         <v>4507</v>
       </c>
-      <c r="M363" s="3" t="s">
+      <c r="M366" s="3" t="s">
         <v>4545</v>
       </c>
-      <c r="N363" s="3" t="s">
+      <c r="N366" s="3" t="s">
         <v>4508</v>
       </c>
-      <c r="O363" s="4" t="s">
+      <c r="O366" s="4" t="s">
         <v>4561</v>
       </c>
-      <c r="P363" s="3" t="s">
+      <c r="P366" s="3" t="s">
         <v>4500</v>
       </c>
     </row>
-    <row r="364" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A364" s="3" t="s">
+    <row r="367" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A367" s="3" t="s">
         <v>4163</v>
       </c>
-      <c r="B364" s="3" t="s">
+      <c r="B367" s="3" t="s">
         <v>4191</v>
       </c>
-      <c r="C364" s="3" t="s">
+      <c r="C367" s="3" t="s">
         <v>4509</v>
       </c>
-      <c r="D364" s="3" t="s">
+      <c r="D367" s="3" t="s">
         <v>4510</v>
       </c>
-      <c r="E364" s="3" t="s">
+      <c r="E367" s="3" t="s">
         <v>4511</v>
       </c>
-      <c r="F364" s="3" t="s">
+      <c r="F367" s="3" t="s">
         <v>4512</v>
       </c>
-      <c r="G364" s="3" t="s">
+      <c r="G367" s="3" t="s">
         <v>4513</v>
       </c>
-      <c r="H364" s="3" t="s">
+      <c r="H367" s="3" t="s">
         <v>4546</v>
       </c>
-      <c r="I364" s="3" t="s">
+      <c r="I367" s="3" t="s">
         <v>4547</v>
       </c>
-      <c r="J364" s="3" t="s">
+      <c r="J367" s="3" t="s">
         <v>4548</v>
       </c>
-      <c r="K364" s="3" t="s">
+      <c r="K367" s="3" t="s">
         <v>4549</v>
       </c>
-      <c r="L364" s="3" t="s">
+      <c r="L367" s="3" t="s">
         <v>4550</v>
       </c>
-      <c r="M364" s="3" t="s">
+      <c r="M367" s="3" t="s">
         <v>4513</v>
       </c>
-      <c r="N364" s="3" t="s">
+      <c r="N367" s="3" t="s">
         <v>4551</v>
       </c>
-      <c r="O364" s="3" t="s">
+      <c r="O367" s="3" t="s">
         <v>4552</v>
       </c>
-      <c r="P364" s="3" t="s">
+      <c r="P367" s="3" t="s">
         <v>4553</v>
       </c>
     </row>
-    <row r="365" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A365" s="3" t="s">
+    <row r="368" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A368" s="3" t="s">
         <v>4164</v>
       </c>
-      <c r="B365" s="3" t="s">
+      <c r="B368" s="3" t="s">
         <v>4192</v>
       </c>
-      <c r="C365" s="3" t="s">
+      <c r="C368" s="3" t="s">
         <v>4562</v>
       </c>
-      <c r="D365" s="3" t="s">
+      <c r="D368" s="3" t="s">
         <v>4563</v>
       </c>
-      <c r="E365" s="3" t="s">
+      <c r="E368" s="3" t="s">
         <v>4564</v>
       </c>
-      <c r="F365" s="3" t="s">
+      <c r="F368" s="3" t="s">
         <v>4565</v>
       </c>
-      <c r="G365" s="3" t="s">
+      <c r="G368" s="3" t="s">
         <v>4566</v>
       </c>
-      <c r="H365" s="3" t="s">
+      <c r="H368" s="3" t="s">
         <v>4567</v>
       </c>
-      <c r="I365" s="3" t="s">
+      <c r="I368" s="3" t="s">
         <v>4568</v>
       </c>
-      <c r="J365" s="3" t="s">
+      <c r="J368" s="3" t="s">
         <v>4569</v>
       </c>
-      <c r="K365" s="3" t="s">
+      <c r="K368" s="3" t="s">
         <v>4570</v>
       </c>
-      <c r="L365" s="3" t="s">
+      <c r="L368" s="3" t="s">
         <v>4571</v>
       </c>
-      <c r="M365" s="3" t="s">
+      <c r="M368" s="3" t="s">
         <v>4572</v>
       </c>
-      <c r="N365" s="3" t="s">
+      <c r="N368" s="3" t="s">
         <v>4573</v>
       </c>
-      <c r="O365" s="3" t="s">
+      <c r="O368" s="3" t="s">
         <v>4603</v>
       </c>
-      <c r="P365" s="3" t="s">
+      <c r="P368" s="3" t="s">
         <v>4574</v>
       </c>
     </row>
-    <row r="366" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A366" s="3" t="s">
+    <row r="369" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A369" s="3" t="s">
         <v>4165</v>
       </c>
-      <c r="B366" s="3" t="s">
+      <c r="B369" s="3" t="s">
         <v>4193</v>
       </c>
-      <c r="C366" s="3" t="s">
+      <c r="C369" s="3" t="s">
         <v>4575</v>
       </c>
-      <c r="D366" s="3" t="s">
+      <c r="D369" s="3" t="s">
         <v>4576</v>
       </c>
-      <c r="E366" s="3" t="s">
+      <c r="E369" s="3" t="s">
         <v>4577</v>
       </c>
-      <c r="F366" s="3" t="s">
+      <c r="F369" s="3" t="s">
         <v>4578</v>
       </c>
-      <c r="G366" s="3" t="s">
+      <c r="G369" s="3" t="s">
         <v>4579</v>
       </c>
-      <c r="H366" s="3" t="s">
+      <c r="H369" s="3" t="s">
         <v>4580</v>
       </c>
-      <c r="I366" s="3" t="s">
+      <c r="I369" s="3" t="s">
         <v>4581</v>
       </c>
-      <c r="J366" s="3" t="s">
+      <c r="J369" s="3" t="s">
         <v>4582</v>
       </c>
-      <c r="K366" s="3" t="s">
+      <c r="K369" s="3" t="s">
         <v>4583</v>
       </c>
-      <c r="L366" s="3" t="s">
+      <c r="L369" s="3" t="s">
         <v>4584</v>
       </c>
-      <c r="M366" s="3" t="s">
+      <c r="M369" s="3" t="s">
         <v>4585</v>
       </c>
-      <c r="N366" s="3" t="s">
+      <c r="N369" s="3" t="s">
         <v>4586</v>
       </c>
-      <c r="O366" s="3" t="s">
+      <c r="O369" s="3" t="s">
         <v>4587</v>
       </c>
-      <c r="P366" s="3" t="s">
+      <c r="P369" s="3" t="s">
         <v>4588</v>
       </c>
     </row>
-    <row r="367" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A367" s="3" t="s">
+    <row r="370" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A370" s="3" t="s">
         <v>4166</v>
       </c>
-      <c r="B367" s="3" t="s">
+      <c r="B370" s="3" t="s">
         <v>4194</v>
       </c>
-      <c r="C367" s="3" t="s">
+      <c r="C370" s="3" t="s">
         <v>4589</v>
       </c>
-      <c r="D367" s="3" t="s">
+      <c r="D370" s="3" t="s">
         <v>4590</v>
       </c>
-      <c r="E367" s="3" t="s">
+      <c r="E370" s="3" t="s">
         <v>4591</v>
       </c>
-      <c r="F367" s="3" t="s">
+      <c r="F370" s="3" t="s">
         <v>4592</v>
       </c>
-      <c r="G367" s="3" t="s">
+      <c r="G370" s="3" t="s">
         <v>4593</v>
       </c>
-      <c r="H367" s="3" t="s">
+      <c r="H370" s="3" t="s">
         <v>4594</v>
       </c>
-      <c r="I367" s="3" t="s">
+      <c r="I370" s="3" t="s">
         <v>4595</v>
       </c>
-      <c r="J367" s="3" t="s">
+      <c r="J370" s="3" t="s">
         <v>4596</v>
       </c>
-      <c r="K367" s="3" t="s">
+      <c r="K370" s="3" t="s">
         <v>4597</v>
       </c>
-      <c r="L367" s="3" t="s">
+      <c r="L370" s="3" t="s">
         <v>4598</v>
       </c>
-      <c r="M367" s="3" t="s">
+      <c r="M370" s="3" t="s">
         <v>4599</v>
       </c>
-      <c r="N367" s="3" t="s">
+      <c r="N370" s="3" t="s">
         <v>4600</v>
       </c>
-      <c r="O367" s="3" t="s">
+      <c r="O370" s="3" t="s">
         <v>4602</v>
       </c>
-      <c r="P367" s="3" t="s">
+      <c r="P370" s="3" t="s">
         <v>4601</v>
       </c>
     </row>
-    <row r="368" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A368" s="3" t="s">
+    <row r="371" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A371" s="3" t="s">
         <v>4167</v>
       </c>
-      <c r="B368" s="3" t="s">
+      <c r="B371" s="3" t="s">
         <v>4177</v>
       </c>
-      <c r="C368" s="3" t="s">
+      <c r="C371" s="3" t="s">
         <v>4605</v>
       </c>
-      <c r="D368" s="3" t="s">
+      <c r="D371" s="3" t="s">
         <v>4606</v>
       </c>
-      <c r="E368" s="3" t="s">
+      <c r="E371" s="3" t="s">
         <v>4607</v>
       </c>
-      <c r="F368" s="3" t="s">
+      <c r="F371" s="3" t="s">
         <v>4608</v>
       </c>
-      <c r="G368" s="3" t="s">
+      <c r="G371" s="3" t="s">
         <v>4613</v>
       </c>
-      <c r="H368" s="3" t="s">
+      <c r="H371" s="3" t="s">
         <v>4611</v>
       </c>
-      <c r="I368" s="3" t="s">
+      <c r="I371" s="3" t="s">
         <v>4609</v>
       </c>
-      <c r="J368" s="3" t="s">
+      <c r="J371" s="3" t="s">
         <v>4610</v>
       </c>
-      <c r="K368" s="3" t="s">
+      <c r="K371" s="3" t="s">
         <v>4612</v>
       </c>
-      <c r="L368" s="3" t="s">
+      <c r="L371" s="3" t="s">
         <v>4614</v>
       </c>
-      <c r="M368" s="3" t="s">
+      <c r="M371" s="3" t="s">
         <v>4613</v>
       </c>
-      <c r="N368" s="3" t="s">
+      <c r="N371" s="3" t="s">
         <v>4615</v>
       </c>
-      <c r="O368" s="3" t="s">
+      <c r="O371" s="3" t="s">
         <v>4616</v>
       </c>
-      <c r="P368" s="3" t="s">
+      <c r="P371" s="3" t="s">
         <v>4617</v>
       </c>
     </row>
-    <row r="369" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A369" s="3" t="s">
+    <row r="372" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A372" s="3" t="s">
         <v>4168</v>
       </c>
-      <c r="B369" s="3" t="s">
+      <c r="B372" s="3" t="s">
         <v>4178</v>
       </c>
-      <c r="C369" s="3" t="s">
+      <c r="C372" s="3" t="s">
         <v>4618</v>
       </c>
-      <c r="D369" s="3" t="s">
+      <c r="D372" s="3" t="s">
         <v>4619</v>
       </c>
-      <c r="E369" s="3" t="s">
+      <c r="E372" s="3" t="s">
         <v>4620</v>
       </c>
-      <c r="F369" s="3" t="s">
+      <c r="F372" s="3" t="s">
         <v>4621</v>
       </c>
-      <c r="G369" s="3" t="s">
+      <c r="G372" s="3" t="s">
         <v>4622</v>
       </c>
-      <c r="H369" s="3" t="s">
+      <c r="H372" s="3" t="s">
         <v>4623</v>
       </c>
-      <c r="I369" s="3" t="s">
+      <c r="I372" s="3" t="s">
         <v>4624</v>
       </c>
-      <c r="J369" s="3" t="s">
+      <c r="J372" s="3" t="s">
         <v>4625</v>
       </c>
-      <c r="K369" s="3" t="s">
+      <c r="K372" s="3" t="s">
         <v>4626</v>
       </c>
-      <c r="L369" s="3" t="s">
+      <c r="L372" s="3" t="s">
         <v>4627</v>
       </c>
-      <c r="M369" s="3" t="s">
+      <c r="M372" s="3" t="s">
         <v>4622</v>
       </c>
-      <c r="N369" s="3" t="s">
+      <c r="N372" s="3" t="s">
         <v>4628</v>
       </c>
-      <c r="O369" s="3" t="s">
+      <c r="O372" s="3" t="s">
         <v>4629</v>
       </c>
-      <c r="P369" s="3" t="s">
+      <c r="P372" s="3" t="s">
         <v>4630</v>
       </c>
     </row>
-    <row r="370" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A370" s="3" t="s">
+    <row r="373" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A373" s="3" t="s">
         <v>4425</v>
       </c>
-      <c r="B370" s="3" t="s">
+      <c r="B373" s="3" t="s">
         <v>4428</v>
       </c>
-      <c r="C370" s="3" t="s">
+      <c r="C373" s="3" t="s">
         <v>4631</v>
       </c>
-      <c r="D370" s="3" t="s">
+      <c r="D373" s="3" t="s">
         <v>4632</v>
       </c>
-      <c r="E370" s="3" t="s">
+      <c r="E373" s="3" t="s">
         <v>4633</v>
       </c>
-      <c r="F370" s="3" t="s">
+      <c r="F373" s="3" t="s">
         <v>4634</v>
       </c>
-      <c r="G370" s="3" t="s">
+      <c r="G373" s="3" t="s">
         <v>4635</v>
       </c>
-      <c r="H370" s="3" t="s">
+      <c r="H373" s="3" t="s">
         <v>4636</v>
       </c>
-      <c r="I370" s="3" t="s">
+      <c r="I373" s="3" t="s">
         <v>4637</v>
       </c>
-      <c r="J370" s="3" t="s">
+      <c r="J373" s="3" t="s">
         <v>4638</v>
       </c>
-      <c r="K370" s="3" t="s">
+      <c r="K373" s="3" t="s">
         <v>4639</v>
       </c>
-      <c r="L370" s="3" t="s">
+      <c r="L373" s="3" t="s">
         <v>4640</v>
       </c>
-      <c r="M370" s="3" t="s">
+      <c r="M373" s="3" t="s">
         <v>4635</v>
       </c>
-      <c r="N370" s="3" t="s">
+      <c r="N373" s="3" t="s">
         <v>4641</v>
       </c>
-      <c r="O370" s="3" t="s">
+      <c r="O373" s="3" t="s">
         <v>4642</v>
       </c>
-      <c r="P370" s="3" t="s">
+      <c r="P373" s="3" t="s">
         <v>4643</v>
       </c>
     </row>
-    <row r="371" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A371" s="3" t="s">
+    <row r="374" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A374" s="3" t="s">
         <v>4426</v>
       </c>
-      <c r="B371" s="3" t="s">
+      <c r="B374" s="3" t="s">
         <v>4430</v>
       </c>
-      <c r="C371" s="3" t="s">
+      <c r="C374" s="3" t="s">
         <v>4644</v>
       </c>
-      <c r="D371" s="3" t="s">
+      <c r="D374" s="3" t="s">
         <v>4645</v>
       </c>
-      <c r="E371" s="3" t="s">
+      <c r="E374" s="3" t="s">
         <v>4646</v>
       </c>
-      <c r="F371" s="3" t="s">
+      <c r="F374" s="3" t="s">
         <v>4647</v>
       </c>
-      <c r="G371" s="3" t="s">
+      <c r="G374" s="3" t="s">
         <v>4648</v>
       </c>
-      <c r="H371" s="3" t="s">
+      <c r="H374" s="3" t="s">
         <v>4649</v>
       </c>
-      <c r="I371" s="3" t="s">
+      <c r="I374" s="3" t="s">
         <v>4650</v>
       </c>
-      <c r="J371" s="3" t="s">
+      <c r="J374" s="3" t="s">
         <v>4651</v>
       </c>
-      <c r="K371" s="3" t="s">
+      <c r="K374" s="3" t="s">
         <v>4652</v>
       </c>
-      <c r="L371" s="3" t="s">
+      <c r="L374" s="3" t="s">
         <v>4653</v>
       </c>
-      <c r="M371" s="3" t="s">
+      <c r="M374" s="3" t="s">
         <v>4654</v>
       </c>
-      <c r="N371" s="3" t="s">
+      <c r="N374" s="3" t="s">
         <v>4655</v>
       </c>
-      <c r="O371" s="3" t="s">
+      <c r="O374" s="3" t="s">
         <v>4656</v>
       </c>
-      <c r="P371" s="3" t="s">
+      <c r="P374" s="3" t="s">
         <v>4657</v>
       </c>
     </row>
-    <row r="372" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A372" s="3" t="s">
+    <row r="375" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A375" s="3" t="s">
         <v>4427</v>
       </c>
-      <c r="B372" s="3" t="s">
+      <c r="B375" s="3" t="s">
         <v>4429</v>
       </c>
-      <c r="C372" s="3" t="s">
+      <c r="C375" s="3" t="s">
         <v>4658</v>
       </c>
-      <c r="D372" s="3" t="s">
+      <c r="D375" s="3" t="s">
         <v>4659</v>
       </c>
-      <c r="E372" s="3" t="s">
+      <c r="E375" s="3" t="s">
         <v>4660</v>
       </c>
-      <c r="F372" s="3" t="s">
+      <c r="F375" s="3" t="s">
         <v>4661</v>
       </c>
-      <c r="G372" s="3" t="s">
+      <c r="G375" s="3" t="s">
         <v>4662</v>
       </c>
-      <c r="H372" s="3" t="s">
+      <c r="H375" s="3" t="s">
         <v>4663</v>
       </c>
-      <c r="I372" s="3" t="s">
+      <c r="I375" s="3" t="s">
         <v>4664</v>
       </c>
-      <c r="J372" s="3" t="s">
+      <c r="J375" s="3" t="s">
         <v>4665</v>
       </c>
-      <c r="K372" s="3" t="s">
+      <c r="K375" s="3" t="s">
         <v>4666</v>
       </c>
-      <c r="L372" s="3" t="s">
+      <c r="L375" s="3" t="s">
         <v>4667</v>
       </c>
-      <c r="M372" s="3" t="s">
+      <c r="M375" s="3" t="s">
         <v>4668</v>
       </c>
-      <c r="N372" s="3" t="s">
+      <c r="N375" s="3" t="s">
         <v>4669</v>
       </c>
-      <c r="O372" s="3" t="s">
+      <c r="O375" s="3" t="s">
         <v>4670</v>
       </c>
-      <c r="P372" s="3" t="s">
+      <c r="P375" s="3" t="s">
         <v>4671</v>
       </c>
     </row>
-    <row r="373" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A373" s="3" t="s">
+    <row r="376" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A376" s="3" t="s">
         <v>4169</v>
       </c>
-      <c r="B373" s="3" t="s">
+      <c r="B376" s="3" t="s">
         <v>4179</v>
       </c>
-      <c r="C373" s="3" t="s">
+      <c r="C376" s="3" t="s">
         <v>4672</v>
       </c>
-      <c r="D373" s="3" t="s">
+      <c r="D376" s="3" t="s">
         <v>4673</v>
       </c>
-      <c r="E373" s="3" t="s">
+      <c r="E376" s="3" t="s">
         <v>4674</v>
       </c>
-      <c r="F373" s="3" t="s">
+      <c r="F376" s="3" t="s">
         <v>4675</v>
       </c>
-      <c r="G373" s="3" t="s">
+      <c r="G376" s="3" t="s">
         <v>4676</v>
       </c>
-      <c r="H373" s="3" t="s">
+      <c r="H376" s="3" t="s">
         <v>4677</v>
       </c>
-      <c r="I373" s="3" t="s">
+      <c r="I376" s="3" t="s">
         <v>4678</v>
       </c>
-      <c r="J373" s="3" t="s">
+      <c r="J376" s="3" t="s">
         <v>4679</v>
       </c>
-      <c r="K373" s="3" t="s">
+      <c r="K376" s="3" t="s">
         <v>4680</v>
       </c>
-      <c r="L373" s="3" t="s">
+      <c r="L376" s="3" t="s">
         <v>4681</v>
       </c>
-      <c r="M373" s="3" t="s">
+      <c r="M376" s="3" t="s">
         <v>4682</v>
       </c>
-      <c r="N373" s="3" t="s">
+      <c r="N376" s="3" t="s">
         <v>4683</v>
       </c>
-      <c r="O373" s="3" t="s">
+      <c r="O376" s="3" t="s">
         <v>4684</v>
       </c>
-      <c r="P373" s="3" t="s">
+      <c r="P376" s="3" t="s">
         <v>4685</v>
       </c>
     </row>
-    <row r="374" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A374" s="3" t="s">
+    <row r="377" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A377" s="3" t="s">
         <v>4170</v>
       </c>
-      <c r="B374" s="3" t="s">
+      <c r="B377" s="3" t="s">
         <v>4180</v>
       </c>
-      <c r="C374" s="3" t="s">
+      <c r="C377" s="3" t="s">
         <v>4686</v>
       </c>
-      <c r="D374" s="3" t="s">
+      <c r="D377" s="3" t="s">
         <v>4687</v>
       </c>
-      <c r="E374" s="3" t="s">
+      <c r="E377" s="3" t="s">
         <v>4688</v>
       </c>
-      <c r="F374" s="3" t="s">
+      <c r="F377" s="3" t="s">
         <v>4689</v>
       </c>
-      <c r="G374" s="3" t="s">
+      <c r="G377" s="3" t="s">
         <v>4690</v>
       </c>
-      <c r="H374" s="3" t="s">
+      <c r="H377" s="3" t="s">
         <v>4691</v>
       </c>
-      <c r="I374" s="3" t="s">
+      <c r="I377" s="3" t="s">
         <v>4692</v>
       </c>
-      <c r="J374" s="3" t="s">
+      <c r="J377" s="3" t="s">
         <v>4693</v>
       </c>
-      <c r="K374" s="3" t="s">
+      <c r="K377" s="3" t="s">
         <v>4694</v>
       </c>
-      <c r="L374" s="3" t="s">
+      <c r="L377" s="3" t="s">
         <v>4695</v>
       </c>
-      <c r="M374" s="3" t="s">
+      <c r="M377" s="3" t="s">
         <v>4690</v>
       </c>
-      <c r="N374" s="3" t="s">
+      <c r="N377" s="3" t="s">
         <v>4696</v>
       </c>
-      <c r="O374" s="3" t="s">
+      <c r="O377" s="3" t="s">
         <v>4697</v>
       </c>
-      <c r="P374" s="3" t="s">
+      <c r="P377" s="3" t="s">
         <v>4698</v>
       </c>
     </row>
-    <row r="375" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A375" s="3" t="s">
+    <row r="378" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A378" s="3" t="s">
         <v>4171</v>
       </c>
-      <c r="B375" s="3" t="s">
+      <c r="B378" s="3" t="s">
         <v>4181</v>
       </c>
-      <c r="C375" s="3" t="s">
+      <c r="C378" s="3" t="s">
         <v>4700</v>
       </c>
-      <c r="D375" s="3" t="s">
+      <c r="D378" s="3" t="s">
         <v>4701</v>
       </c>
-      <c r="E375" s="3" t="s">
+      <c r="E378" s="3" t="s">
         <v>4702</v>
       </c>
-      <c r="F375" s="3" t="s">
+      <c r="F378" s="3" t="s">
         <v>4703</v>
       </c>
-      <c r="G375" s="3" t="s">
+      <c r="G378" s="3" t="s">
         <v>4704</v>
       </c>
-      <c r="H375" s="3" t="s">
+      <c r="H378" s="3" t="s">
         <v>4705</v>
       </c>
-      <c r="I375" s="3" t="s">
+      <c r="I378" s="3" t="s">
         <v>4706</v>
       </c>
-      <c r="J375" s="3" t="s">
+      <c r="J378" s="3" t="s">
         <v>4707</v>
       </c>
-      <c r="K375" s="3" t="s">
+      <c r="K378" s="3" t="s">
         <v>4708</v>
       </c>
-      <c r="L375" s="3" t="s">
+      <c r="L378" s="3" t="s">
         <v>4709</v>
       </c>
-      <c r="M375" s="3" t="s">
+      <c r="M378" s="3" t="s">
         <v>4704</v>
       </c>
-      <c r="N375" s="3" t="s">
+      <c r="N378" s="3" t="s">
         <v>4710</v>
       </c>
-      <c r="O375" s="3" t="s">
+      <c r="O378" s="3" t="s">
         <v>4711</v>
       </c>
-      <c r="P375" s="3" t="s">
+      <c r="P378" s="3" t="s">
         <v>4712</v>
       </c>
     </row>
-    <row r="376" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A376" s="3" t="s">
+    <row r="379" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A379" s="3" t="s">
         <v>4172</v>
       </c>
-      <c r="B376" s="3" t="s">
+      <c r="B379" s="3" t="s">
         <v>4195</v>
       </c>
-      <c r="C376" s="3" t="s">
+      <c r="C379" s="3" t="s">
         <v>4699</v>
       </c>
-      <c r="D376" s="3" t="s">
+      <c r="D379" s="3" t="s">
         <v>4718</v>
       </c>
-      <c r="E376" s="3" t="s">
+      <c r="E379" s="3" t="s">
         <v>4719</v>
       </c>
-      <c r="F376" s="3" t="s">
+      <c r="F379" s="3" t="s">
         <v>4720</v>
       </c>
-      <c r="G376" s="3" t="s">
+      <c r="G379" s="3" t="s">
         <v>4716</v>
       </c>
-      <c r="H376" s="3" t="s">
+      <c r="H379" s="3" t="s">
         <v>4721</v>
       </c>
-      <c r="I376" s="3" t="s">
+      <c r="I379" s="3" t="s">
         <v>4722</v>
       </c>
-      <c r="J376" s="3" t="s">
+      <c r="J379" s="3" t="s">
         <v>4723</v>
       </c>
-      <c r="K376" s="3" t="s">
+      <c r="K379" s="3" t="s">
         <v>4716</v>
       </c>
-      <c r="L376" s="3" t="s">
+      <c r="L379" s="3" t="s">
         <v>4717</v>
       </c>
-      <c r="M376" s="3" t="s">
+      <c r="M379" s="3" t="s">
         <v>4716</v>
       </c>
-      <c r="N376" s="3" t="s">
+      <c r="N379" s="3" t="s">
         <v>4715</v>
       </c>
-      <c r="O376" s="3" t="s">
+      <c r="O379" s="3" t="s">
         <v>4714</v>
       </c>
-      <c r="P376" s="3" t="s">
+      <c r="P379" s="3" t="s">
         <v>4713</v>
       </c>
     </row>
-    <row r="377" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="378" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A378" s="3" t="s">
+    <row r="380" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="381" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A381" s="3" t="s">
         <v>2395</v>
       </c>
-      <c r="B378" s="3" t="s">
+      <c r="B381" s="3" t="s">
         <v>3811</v>
       </c>
-      <c r="C378" s="3" t="s">
+      <c r="C381" s="3" t="s">
         <v>3809</v>
       </c>
-      <c r="D378" s="3" t="s">
+      <c r="D381" s="3" t="s">
         <v>3810</v>
       </c>
-      <c r="E378" s="3" t="s">
+      <c r="E381" s="3" t="s">
         <v>3812</v>
       </c>
-      <c r="F378" s="3" t="s">
+      <c r="F381" s="3" t="s">
         <v>3813</v>
       </c>
-      <c r="G378" s="3" t="s">
+      <c r="G381" s="3" t="s">
         <v>3814</v>
       </c>
-      <c r="H378" s="3" t="s">
+      <c r="H381" s="3" t="s">
         <v>3815</v>
       </c>
-      <c r="I378" s="3" t="s">
+      <c r="I381" s="3" t="s">
         <v>3816</v>
       </c>
-      <c r="J378" s="3" t="s">
+      <c r="J381" s="3" t="s">
         <v>3817</v>
       </c>
-      <c r="K378" s="3" t="s">
+      <c r="K381" s="3" t="s">
         <v>3818</v>
       </c>
-      <c r="L378" s="3" t="s">
+      <c r="L381" s="3" t="s">
         <v>3819</v>
       </c>
-      <c r="M378" s="3" t="s">
+      <c r="M381" s="3" t="s">
         <v>3820</v>
       </c>
-      <c r="N378" s="3" t="s">
+      <c r="N381" s="3" t="s">
         <v>3821</v>
       </c>
-      <c r="O378" s="3" t="s">
+      <c r="O381" s="3" t="s">
         <v>3822</v>
       </c>
-      <c r="P378" s="3" t="s">
+      <c r="P381" s="3" t="s">
         <v>3823</v>
       </c>
     </row>
-    <row r="379" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="380" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A380" s="3" t="s">
+    <row r="382" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="383" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A383" s="3" t="s">
         <v>3969</v>
       </c>
-      <c r="B380" s="3" t="s">
+      <c r="B383" s="3" t="s">
         <v>3971</v>
       </c>
-      <c r="C380" s="3" t="s">
+      <c r="C383" s="3" t="s">
         <v>3976</v>
       </c>
-      <c r="D380" s="3" t="s">
+      <c r="D383" s="3" t="s">
         <v>3977</v>
       </c>
-      <c r="E380" s="3" t="s">
+      <c r="E383" s="3" t="s">
         <v>3978</v>
       </c>
-      <c r="F380" s="3" t="s">
+      <c r="F383" s="3" t="s">
         <v>3979</v>
       </c>
-      <c r="G380" s="3" t="s">
+      <c r="G383" s="3" t="s">
         <v>3980</v>
       </c>
-      <c r="H380" s="3" t="s">
+      <c r="H383" s="3" t="s">
         <v>3981</v>
       </c>
-      <c r="I380" s="3" t="s">
+      <c r="I383" s="3" t="s">
         <v>3982</v>
       </c>
-      <c r="J380" s="3" t="s">
+      <c r="J383" s="3" t="s">
         <v>3983</v>
       </c>
-      <c r="K380" s="3" t="s">
+      <c r="K383" s="3" t="s">
         <v>3984</v>
       </c>
-      <c r="L380" s="3" t="s">
+      <c r="L383" s="3" t="s">
         <v>3985</v>
       </c>
-      <c r="M380" s="3" t="s">
+      <c r="M383" s="3" t="s">
         <v>3986</v>
       </c>
-      <c r="N380" s="3" t="s">
+      <c r="N383" s="3" t="s">
         <v>3975</v>
       </c>
-      <c r="O380" s="3" t="s">
+      <c r="O383" s="3" t="s">
         <v>3974</v>
       </c>
-      <c r="P380" s="3" t="s">
+      <c r="P383" s="3" t="s">
         <v>3973</v>
       </c>
     </row>
-    <row r="381" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="3" t="s">
+    <row r="384" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A384" s="3" t="s">
         <v>3970</v>
       </c>
-      <c r="B381" s="3" t="s">
+      <c r="B384" s="3" t="s">
         <v>3972</v>
       </c>
-      <c r="C381" s="3" t="s">
+      <c r="C384" s="3" t="s">
         <v>3992</v>
       </c>
-      <c r="D381" s="3" t="s">
+      <c r="D384" s="3" t="s">
         <v>3993</v>
       </c>
-      <c r="E381" s="3" t="s">
+      <c r="E384" s="3" t="s">
         <v>3994</v>
       </c>
-      <c r="F381" s="3" t="s">
+      <c r="F384" s="3" t="s">
         <v>3995</v>
       </c>
-      <c r="G381" s="3" t="s">
+      <c r="G384" s="3" t="s">
         <v>3996</v>
       </c>
-      <c r="H381" s="3" t="s">
+      <c r="H384" s="3" t="s">
         <v>3997</v>
       </c>
-      <c r="I381" s="3" t="s">
+      <c r="I384" s="3" t="s">
         <v>3998</v>
       </c>
-      <c r="J381" s="3" t="s">
+      <c r="J384" s="3" t="s">
         <v>3999</v>
       </c>
-      <c r="K381" s="3" t="s">
+      <c r="K384" s="3" t="s">
         <v>4000</v>
       </c>
-      <c r="L381" s="3" t="s">
+      <c r="L384" s="3" t="s">
         <v>3988</v>
       </c>
-      <c r="M381" s="3" t="s">
+      <c r="M384" s="3" t="s">
         <v>3987</v>
       </c>
-      <c r="N381" s="3" t="s">
+      <c r="N384" s="3" t="s">
         <v>3989</v>
       </c>
-      <c r="O381" s="3" t="s">
+      <c r="O384" s="3" t="s">
         <v>3990</v>
       </c>
-      <c r="P381" s="3" t="s">
+      <c r="P384" s="3" t="s">
         <v>3991</v>
       </c>
     </row>
-    <row r="382" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="3" t="s">
+    <row r="385" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A385" s="3" t="s">
         <v>4990</v>
       </c>
-      <c r="B382" s="3" t="s">
+      <c r="B385" s="3" t="s">
         <v>4991</v>
       </c>
-      <c r="C382" s="3" t="s">
+      <c r="C385" s="3" t="s">
         <v>4992</v>
       </c>
-      <c r="D382" s="3" t="s">
+      <c r="D385" s="3" t="s">
         <v>4993</v>
       </c>
-      <c r="E382" s="3" t="s">
+      <c r="E385" s="3" t="s">
         <v>5005</v>
       </c>
-      <c r="F382" s="3" t="s">
+      <c r="F385" s="3" t="s">
         <v>4994</v>
       </c>
-      <c r="G382" s="3" t="s">
+      <c r="G385" s="3" t="s">
         <v>5001</v>
       </c>
-      <c r="H382" s="3" t="s">
+      <c r="H385" s="3" t="s">
         <v>4998</v>
       </c>
-      <c r="I382" s="3" t="s">
+      <c r="I385" s="3" t="s">
         <v>4995</v>
       </c>
-      <c r="J382" s="3" t="s">
+      <c r="J385" s="3" t="s">
         <v>4999</v>
       </c>
-      <c r="K382" s="3" t="s">
+      <c r="K385" s="3" t="s">
         <v>5000</v>
       </c>
-      <c r="L382" s="3" t="s">
+      <c r="L385" s="3" t="s">
         <v>4996</v>
       </c>
-      <c r="M382" s="3" t="s">
+      <c r="M385" s="3" t="s">
         <v>4997</v>
       </c>
-      <c r="N382" s="3" t="s">
+      <c r="N385" s="3" t="s">
         <v>5002</v>
       </c>
-      <c r="O382" s="3" t="s">
+      <c r="O385" s="3" t="s">
         <v>5003</v>
       </c>
-      <c r="P382" s="3" t="s">
+      <c r="P385" s="3" t="s">
         <v>5004</v>
       </c>
     </row>
-    <row r="383" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A383" s="3" t="s">
+    <row r="386" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A386" s="3" t="s">
         <v>4989</v>
       </c>
-      <c r="B383" s="3" t="s">
+      <c r="B386" s="3" t="s">
         <v>5008</v>
       </c>
-      <c r="C383" s="3" t="s">
+      <c r="C386" s="3" t="s">
         <v>5007</v>
       </c>
-      <c r="D383" s="3" t="s">
+      <c r="D386" s="3" t="s">
         <v>5006</v>
       </c>
-      <c r="E383" s="3" t="s">
+      <c r="E386" s="3" t="s">
         <v>5009</v>
       </c>
-      <c r="F383" s="3" t="s">
+      <c r="F386" s="3" t="s">
         <v>5010</v>
       </c>
-      <c r="G383" s="3" t="s">
+      <c r="G386" s="3" t="s">
         <v>5011</v>
       </c>
-      <c r="H383" s="3" t="s">
+      <c r="H386" s="3" t="s">
         <v>5012</v>
       </c>
-      <c r="I383" s="3" t="s">
+      <c r="I386" s="3" t="s">
         <v>5013</v>
       </c>
-      <c r="J383" s="3" t="s">
+      <c r="J386" s="3" t="s">
         <v>5014</v>
       </c>
-      <c r="K383" s="3" t="s">
+      <c r="K386" s="3" t="s">
         <v>5015</v>
       </c>
-      <c r="L383" s="3" t="s">
+      <c r="L386" s="3" t="s">
         <v>5016</v>
       </c>
-      <c r="M383" s="3" t="s">
+      <c r="M386" s="3" t="s">
         <v>5017</v>
       </c>
-      <c r="N383" s="3" t="s">
+      <c r="N386" s="3" t="s">
         <v>5018</v>
       </c>
-      <c r="O383" s="3" t="s">
+      <c r="O386" s="3" t="s">
         <v>5019</v>
       </c>
-      <c r="P383" s="3" t="s">
+      <c r="P386" s="3" t="s">
         <v>5020</v>
       </c>
     </row>
-    <row r="384" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="385" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A385" s="3" t="s">
+    <row r="387" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="388" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A388" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B385" s="3" t="s">
+      <c r="B388" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C385" s="3" t="s">
+      <c r="C388" s="3" t="s">
         <v>1471</v>
       </c>
-      <c r="D385" s="3" t="s">
+      <c r="D388" s="3" t="s">
         <v>1685</v>
       </c>
-      <c r="E385" s="3" t="s">
+      <c r="E388" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="F385" s="3" t="s">
+      <c r="F388" s="3" t="s">
         <v>1694</v>
       </c>
-      <c r="G385" s="3" t="s">
+      <c r="G388" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H385" s="3" t="s">
+      <c r="H388" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I385" s="3" t="s">
+      <c r="I388" s="3" t="s">
         <v>1801</v>
       </c>
-      <c r="J385" s="3" t="s">
+      <c r="J388" s="3" t="s">
         <v>2218</v>
       </c>
-      <c r="K385" s="3" t="s">
+      <c r="K388" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="L385" s="3" t="s">
+      <c r="L388" s="3" t="s">
         <v>813</v>
       </c>
-      <c r="M385" s="3" t="s">
+      <c r="M388" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="N385" s="3" t="s">
+      <c r="N388" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="O385" s="3" t="s">
+      <c r="O388" s="3" t="s">
         <v>895</v>
       </c>
-      <c r="P385" s="3" t="s">
+      <c r="P388" s="3" t="s">
         <v>2216</v>
       </c>
     </row>
-    <row r="386" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A386" s="3" t="s">
+    <row r="389" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A389" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B386" s="3" t="s">
+      <c r="B389" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C386" s="3" t="s">
+      <c r="C389" s="3" t="s">
         <v>1548</v>
       </c>
-      <c r="D386" s="3" t="s">
+      <c r="D389" s="3" t="s">
         <v>1799</v>
       </c>
-      <c r="E386" s="3" t="s">
+      <c r="E389" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F386" s="3" t="s">
+      <c r="F389" s="3" t="s">
         <v>1800</v>
       </c>
-      <c r="G386" s="3" t="s">
+      <c r="G389" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="H386" s="3" t="s">
+      <c r="H389" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I386" s="3" t="s">
+      <c r="I389" s="3" t="s">
         <v>1802</v>
       </c>
-      <c r="J386" s="3" t="s">
+      <c r="J389" s="3" t="s">
         <v>2219</v>
       </c>
-      <c r="K386" s="3" t="s">
+      <c r="K389" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="L386" s="3" t="s">
+      <c r="L389" s="3" t="s">
         <v>869</v>
       </c>
-      <c r="M386" s="3" t="s">
+      <c r="M389" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="N386" s="3" t="s">
+      <c r="N389" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="O386" s="3" t="s">
+      <c r="O389" s="3" t="s">
         <v>932</v>
       </c>
-      <c r="P386" s="3" t="s">
+      <c r="P389" s="3" t="s">
         <v>2217</v>
       </c>
     </row>
-    <row r="387" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A387" s="3" t="s">
+    <row r="390" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A390" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B387" s="3" t="s">
+      <c r="B390" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C387" s="3" t="s">
+      <c r="C390" s="3" t="s">
         <v>1549</v>
       </c>
-      <c r="D387" s="3" t="s">
+      <c r="D390" s="3" t="s">
         <v>1804</v>
       </c>
-      <c r="E387" s="3" t="s">
+      <c r="E390" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="F387" s="3" t="s">
+      <c r="F390" s="3" t="s">
         <v>1805</v>
       </c>
-      <c r="G387" s="3" t="s">
+      <c r="G390" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H387" s="3" t="s">
+      <c r="H390" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="I387" s="3" t="s">
+      <c r="I390" s="3" t="s">
         <v>1803</v>
       </c>
-      <c r="J387" s="3" t="s">
+      <c r="J390" s="3" t="s">
         <v>2220</v>
       </c>
-      <c r="K387" s="3" t="s">
+      <c r="K390" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="L387" s="3" t="s">
+      <c r="L390" s="3" t="s">
         <v>870</v>
       </c>
-      <c r="M387" s="3" t="s">
+      <c r="M390" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="N387" s="3" t="s">
+      <c r="N390" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="O387" s="3" t="s">
+      <c r="O390" s="3" t="s">
         <v>933</v>
       </c>
-      <c r="P387" s="3" t="s">
+      <c r="P390" s="3" t="s">
         <v>2221</v>
       </c>
     </row>
-    <row r="388" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="389" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A389" s="3" t="s">
+    <row r="391" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="392" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A392" s="3" t="s">
         <v>3622</v>
       </c>
-      <c r="B389" s="3" t="s">
+      <c r="B392" s="3" t="s">
         <v>3624</v>
       </c>
-      <c r="C389" s="3" t="s">
+      <c r="C392" s="3" t="s">
         <v>1469</v>
       </c>
-      <c r="D389" s="3" t="s">
+      <c r="D392" s="3" t="s">
         <v>1683</v>
       </c>
-      <c r="E389" s="3" t="s">
+      <c r="E392" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="F389" s="3" t="s">
+      <c r="F392" s="3" t="s">
         <v>1692</v>
       </c>
-      <c r="G389" s="3" t="s">
+      <c r="G392" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="H389" s="3" t="s">
+      <c r="H392" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="I389" s="3" t="s">
+      <c r="I392" s="3" t="s">
         <v>1701</v>
       </c>
-      <c r="J389" s="3" t="s">
+      <c r="J392" s="3" t="s">
         <v>2101</v>
       </c>
-      <c r="K389" s="3" t="s">
+      <c r="K392" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="L389" s="3" t="s">
+      <c r="L392" s="3" t="s">
         <v>811</v>
       </c>
-      <c r="M389" s="3" t="s">
+      <c r="M392" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="N389" s="3" t="s">
+      <c r="N392" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="O389" s="3" t="s">
+      <c r="O392" s="3" t="s">
         <v>893</v>
       </c>
-      <c r="P389" s="3" t="s">
+      <c r="P392" s="3" t="s">
         <v>2094</v>
       </c>
     </row>
-    <row r="390" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A390" s="3" t="s">
+    <row r="393" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A393" s="3" t="s">
         <v>3623</v>
       </c>
-      <c r="B390" s="3" t="s">
+      <c r="B393" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C390" s="3" t="s">
+      <c r="C393" s="3" t="s">
         <v>1547</v>
       </c>
-      <c r="D390" s="3" t="s">
+      <c r="D393" s="3" t="s">
         <v>1806</v>
       </c>
-      <c r="E390" s="3" t="s">
+      <c r="E393" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="F390" s="3" t="s">
+      <c r="F393" s="3" t="s">
         <v>1807</v>
       </c>
-      <c r="G390" s="3" t="s">
+      <c r="G393" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="H390" s="3" t="s">
+      <c r="H393" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="I390" s="3" t="s">
+      <c r="I393" s="3" t="s">
         <v>1808</v>
       </c>
-      <c r="J390" s="3" t="s">
+      <c r="J393" s="3" t="s">
         <v>2223</v>
       </c>
-      <c r="K390" s="3" t="s">
+      <c r="K393" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="L390" s="3" t="s">
+      <c r="L393" s="3" t="s">
         <v>871</v>
       </c>
-      <c r="M390" s="3" t="s">
+      <c r="M393" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="N390" s="3" t="s">
+      <c r="N393" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="O390" s="3" t="s">
+      <c r="O393" s="3" t="s">
         <v>934</v>
       </c>
-      <c r="P390" s="3" t="s">
+      <c r="P393" s="3" t="s">
         <v>2222</v>
       </c>
     </row>
-    <row r="391" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="392" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A392" s="3" t="s">
+    <row r="394" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="395" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A395" s="3" t="s">
         <v>3626</v>
       </c>
-      <c r="B392" s="3" t="s">
+      <c r="B395" s="3" t="s">
         <v>3625</v>
       </c>
-      <c r="C392" s="3" t="s">
+      <c r="C395" s="3" t="s">
         <v>3671</v>
       </c>
-      <c r="D392" s="3" t="s">
+      <c r="D395" s="3" t="s">
         <v>3658</v>
       </c>
-      <c r="E392" s="3" t="s">
+      <c r="E395" s="3" t="s">
         <v>3659</v>
       </c>
-      <c r="F392" s="3" t="s">
+      <c r="F395" s="3" t="s">
         <v>3660</v>
       </c>
-      <c r="G392" s="3" t="s">
+      <c r="G395" s="3" t="s">
         <v>3661</v>
       </c>
-      <c r="H392" s="3" t="s">
+      <c r="H395" s="3" t="s">
         <v>3662</v>
       </c>
-      <c r="I392" s="3" t="s">
+      <c r="I395" s="3" t="s">
         <v>3663</v>
       </c>
-      <c r="J392" s="3" t="s">
+      <c r="J395" s="3" t="s">
         <v>3664</v>
       </c>
-      <c r="K392" s="3" t="s">
+      <c r="K395" s="3" t="s">
         <v>3665</v>
       </c>
-      <c r="L392" s="3" t="s">
+      <c r="L395" s="3" t="s">
         <v>3666</v>
       </c>
-      <c r="M392" s="3" t="s">
+      <c r="M395" s="3" t="s">
         <v>3667</v>
       </c>
-      <c r="N392" s="3" t="s">
+      <c r="N395" s="3" t="s">
         <v>3668</v>
       </c>
-      <c r="O392" s="3" t="s">
+      <c r="O395" s="3" t="s">
         <v>3669</v>
       </c>
-      <c r="P392" s="3" t="s">
+      <c r="P395" s="3" t="s">
         <v>3670</v>
       </c>
     </row>
-    <row r="393" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A393" s="3" t="s">
+    <row r="396" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A396" s="3" t="s">
         <v>3627</v>
       </c>
-      <c r="B393" s="3" t="s">
+      <c r="B396" s="3" t="s">
         <v>2380</v>
       </c>
-      <c r="C393" s="3" t="s">
+      <c r="C396" s="3" t="s">
         <v>2381</v>
       </c>
-      <c r="D393" s="3" t="s">
+      <c r="D396" s="3" t="s">
         <v>2382</v>
       </c>
-      <c r="E393" s="3" t="s">
+      <c r="E396" s="3" t="s">
         <v>2384</v>
       </c>
-      <c r="F393" s="3" t="s">
+      <c r="F396" s="3" t="s">
         <v>2385</v>
       </c>
-      <c r="G393" s="4" t="s">
+      <c r="G396" s="4" t="s">
         <v>2386</v>
       </c>
-      <c r="H393" s="3" t="s">
+      <c r="H396" s="3" t="s">
         <v>2387</v>
       </c>
-      <c r="I393" s="3" t="s">
+      <c r="I396" s="3" t="s">
         <v>2388</v>
       </c>
-      <c r="J393" s="3" t="s">
+      <c r="J396" s="3" t="s">
         <v>2389</v>
       </c>
-      <c r="K393" s="3" t="s">
+      <c r="K396" s="3" t="s">
         <v>2390</v>
       </c>
-      <c r="L393" s="3" t="s">
+      <c r="L396" s="3" t="s">
         <v>2391</v>
       </c>
-      <c r="M393" s="3" t="s">
+      <c r="M396" s="3" t="s">
         <v>2392</v>
       </c>
-      <c r="N393" s="3" t="s">
+      <c r="N396" s="3" t="s">
         <v>2393</v>
       </c>
-      <c r="O393" s="3" t="s">
+      <c r="O396" s="3" t="s">
         <v>2394</v>
       </c>
-      <c r="P393" s="3" t="s">
+      <c r="P396" s="3" t="s">
         <v>2383</v>
       </c>
     </row>
-    <row r="394" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="G394" s="4"/>
-    </row>
-    <row r="395" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A395" s="3" t="s">
+    <row r="397" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="G397" s="4"/>
+    </row>
+    <row r="398" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A398" s="3" t="s">
         <v>3636</v>
       </c>
-      <c r="B395" s="3" t="s">
+      <c r="B398" s="3" t="s">
         <v>3634</v>
       </c>
-      <c r="C395" s="3" t="s">
+      <c r="C398" s="3" t="s">
         <v>3672</v>
       </c>
-      <c r="D395" s="3" t="s">
+      <c r="D398" s="3" t="s">
         <v>3699</v>
       </c>
-      <c r="E395" s="3" t="s">
+      <c r="E398" s="3" t="s">
         <v>3678</v>
       </c>
-      <c r="F395" s="3" t="s">
+      <c r="F398" s="3" t="s">
         <v>3707</v>
       </c>
-      <c r="G395" s="4" t="s">
+      <c r="G398" s="4" t="s">
         <v>3677</v>
       </c>
-      <c r="H395" s="3" t="s">
+      <c r="H398" s="3" t="s">
         <v>3676</v>
       </c>
-      <c r="I395" s="3" t="s">
+      <c r="I398" s="3" t="s">
         <v>3708</v>
       </c>
-      <c r="J395" s="3" t="s">
+      <c r="J398" s="3" t="s">
         <v>3712</v>
       </c>
-      <c r="K395" s="3" t="s">
+      <c r="K398" s="3" t="s">
         <v>3675</v>
       </c>
-      <c r="L395" s="3" t="s">
+      <c r="L398" s="3" t="s">
         <v>3716</v>
       </c>
-      <c r="M395" s="3" t="s">
+      <c r="M398" s="3" t="s">
         <v>3674</v>
       </c>
-      <c r="N395" s="3" t="s">
+      <c r="N398" s="3" t="s">
         <v>3720</v>
       </c>
-      <c r="O395" s="3" t="s">
+      <c r="O398" s="3" t="s">
         <v>3726</v>
       </c>
-      <c r="P395" s="3" t="s">
+      <c r="P398" s="3" t="s">
         <v>3673</v>
       </c>
     </row>
-    <row r="396" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A396" s="3" t="s">
+    <row r="399" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A399" s="3" t="s">
         <v>3637</v>
       </c>
-      <c r="B396" s="3" t="s">
+      <c r="B399" s="3" t="s">
         <v>3635</v>
       </c>
-      <c r="C396" s="3" t="s">
+      <c r="C399" s="3" t="s">
         <v>3685</v>
       </c>
-      <c r="D396" s="3" t="s">
+      <c r="D399" s="3" t="s">
         <v>3700</v>
       </c>
-      <c r="E396" s="3" t="s">
+      <c r="E399" s="3" t="s">
         <v>3679</v>
       </c>
-      <c r="F396" s="3" t="s">
+      <c r="F399" s="3" t="s">
         <v>3706</v>
       </c>
-      <c r="G396" s="4" t="s">
+      <c r="G399" s="4" t="s">
         <v>3680</v>
       </c>
-      <c r="H396" s="3" t="s">
+      <c r="H399" s="3" t="s">
         <v>3681</v>
       </c>
-      <c r="I396" s="3" t="s">
+      <c r="I399" s="3" t="s">
         <v>3709</v>
       </c>
-      <c r="J396" s="3" t="s">
+      <c r="J399" s="3" t="s">
         <v>3713</v>
       </c>
-      <c r="K396" s="3" t="s">
+      <c r="K399" s="3" t="s">
         <v>3682</v>
       </c>
-      <c r="L396" s="3" t="s">
+      <c r="L399" s="3" t="s">
         <v>3717</v>
       </c>
-      <c r="M396" s="3" t="s">
+      <c r="M399" s="3" t="s">
         <v>3683</v>
       </c>
-      <c r="N396" s="3" t="s">
+      <c r="N399" s="3" t="s">
         <v>3721</v>
       </c>
-      <c r="O396" s="3" t="s">
+      <c r="O399" s="3" t="s">
         <v>3727</v>
       </c>
-      <c r="P396" s="3" t="s">
+      <c r="P399" s="3" t="s">
         <v>3684</v>
       </c>
     </row>
-    <row r="397" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A397" s="3" t="s">
+    <row r="400" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A400" s="3" t="s">
         <v>3654</v>
       </c>
-      <c r="B397" s="3" t="s">
+      <c r="B400" s="3" t="s">
         <v>3655</v>
       </c>
-      <c r="C397" s="3" t="s">
+      <c r="C400" s="3" t="s">
         <v>3686</v>
       </c>
-      <c r="D397" s="3" t="s">
+      <c r="D400" s="3" t="s">
         <v>3701</v>
       </c>
-      <c r="E397" s="3" t="s">
+      <c r="E400" s="3" t="s">
         <v>3692</v>
       </c>
-      <c r="F397" s="3" t="s">
+      <c r="F400" s="3" t="s">
         <v>3705</v>
       </c>
-      <c r="G397" s="4" t="s">
+      <c r="G400" s="4" t="s">
         <v>3690</v>
       </c>
-      <c r="H397" s="3" t="s">
+      <c r="H400" s="3" t="s">
         <v>3691</v>
       </c>
-      <c r="I397" s="3" t="s">
+      <c r="I400" s="3" t="s">
         <v>3710</v>
       </c>
-      <c r="J397" s="3" t="s">
+      <c r="J400" s="3" t="s">
         <v>3714</v>
       </c>
-      <c r="K397" s="3" t="s">
+      <c r="K400" s="3" t="s">
         <v>3688</v>
       </c>
-      <c r="L397" s="3" t="s">
+      <c r="L400" s="3" t="s">
         <v>3718</v>
       </c>
-      <c r="M397" s="3" t="s">
+      <c r="M400" s="3" t="s">
         <v>3689</v>
       </c>
-      <c r="N397" s="3" t="s">
+      <c r="N400" s="3" t="s">
         <v>3722</v>
       </c>
-      <c r="O397" s="3" t="s">
+      <c r="O400" s="3" t="s">
         <v>3724</v>
       </c>
-      <c r="P397" s="3" t="s">
+      <c r="P400" s="3" t="s">
         <v>3687</v>
       </c>
     </row>
-    <row r="398" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A398" s="3" t="s">
+    <row r="401" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A401" s="3" t="s">
         <v>3656</v>
       </c>
-      <c r="B398" s="3" t="s">
+      <c r="B401" s="3" t="s">
         <v>3657</v>
       </c>
-      <c r="C398" s="3" t="s">
+      <c r="C401" s="3" t="s">
         <v>3703</v>
       </c>
-      <c r="D398" s="3" t="s">
+      <c r="D401" s="3" t="s">
         <v>3702</v>
       </c>
-      <c r="E398" s="3" t="s">
+      <c r="E401" s="3" t="s">
         <v>3693</v>
       </c>
-      <c r="F398" s="3" t="s">
+      <c r="F401" s="3" t="s">
         <v>3704</v>
       </c>
-      <c r="G398" s="4" t="s">
+      <c r="G401" s="4" t="s">
         <v>3695</v>
       </c>
-      <c r="H398" s="3" t="s">
+      <c r="H401" s="3" t="s">
         <v>3694</v>
       </c>
-      <c r="I398" s="3" t="s">
+      <c r="I401" s="3" t="s">
         <v>3711</v>
       </c>
-      <c r="J398" s="3" t="s">
+      <c r="J401" s="3" t="s">
         <v>3715</v>
       </c>
-      <c r="K398" s="3" t="s">
+      <c r="K401" s="3" t="s">
         <v>3696</v>
       </c>
-      <c r="L398" s="3" t="s">
+      <c r="L401" s="3" t="s">
         <v>3719</v>
       </c>
-      <c r="M398" s="3" t="s">
+      <c r="M401" s="3" t="s">
         <v>3697</v>
       </c>
-      <c r="N398" s="3" t="s">
+      <c r="N401" s="3" t="s">
         <v>3723</v>
       </c>
-      <c r="O398" s="3" t="s">
+      <c r="O401" s="3" t="s">
         <v>3725</v>
       </c>
-      <c r="P398" s="3" t="s">
+      <c r="P401" s="3" t="s">
         <v>3698</v>
       </c>
     </row>
-    <row r="399" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A399" s="3" t="s">
+    <row r="402" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A402" s="3" t="s">
         <v>3642</v>
       </c>
-      <c r="B399" s="3" t="s">
+      <c r="B402" s="3" t="s">
         <v>2411</v>
       </c>
-      <c r="C399" s="3" t="s">
+      <c r="C402" s="3" t="s">
         <v>2568</v>
       </c>
-      <c r="D399" s="3" t="s">
+      <c r="D402" s="3" t="s">
         <v>2567</v>
       </c>
-      <c r="E399" s="3" t="s">
+      <c r="E402" s="3" t="s">
         <v>2426</v>
       </c>
-      <c r="F399" s="3" t="s">
+      <c r="F402" s="3" t="s">
         <v>2542</v>
       </c>
-      <c r="G399" s="3" t="s">
+      <c r="G402" s="3" t="s">
         <v>2436</v>
       </c>
-      <c r="H399" s="3" t="s">
+      <c r="H402" s="3" t="s">
         <v>2447</v>
       </c>
-      <c r="I399" s="3" t="s">
+      <c r="I402" s="3" t="s">
         <v>2529</v>
       </c>
-      <c r="J399" s="3" t="s">
+      <c r="J402" s="3" t="s">
         <v>2516</v>
       </c>
-      <c r="K399" s="3" t="s">
+      <c r="K402" s="3" t="s">
         <v>2458</v>
       </c>
-      <c r="L399" s="3" t="s">
+      <c r="L402" s="3" t="s">
         <v>2504</v>
       </c>
-      <c r="M399" s="3" t="s">
+      <c r="M402" s="3" t="s">
         <v>2477</v>
       </c>
-      <c r="N399" s="3" t="s">
+      <c r="N402" s="3" t="s">
         <v>2478</v>
       </c>
-      <c r="O399" s="3" t="s">
+      <c r="O402" s="3" t="s">
         <v>2490</v>
       </c>
-      <c r="P399" s="3" t="s">
+      <c r="P402" s="3" t="s">
         <v>2581</v>
       </c>
     </row>
-    <row r="400" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A400" s="3" t="s">
+    <row r="403" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A403" s="3" t="s">
         <v>3643</v>
       </c>
-      <c r="B400" s="3" t="s">
+      <c r="B403" s="3" t="s">
         <v>2415</v>
       </c>
-      <c r="C400" s="3" t="s">
+      <c r="C403" s="3" t="s">
         <v>2569</v>
       </c>
-      <c r="D400" s="3" t="s">
+      <c r="D403" s="3" t="s">
         <v>2555</v>
       </c>
-      <c r="E400" s="3" t="s">
+      <c r="E403" s="3" t="s">
         <v>2415</v>
       </c>
-      <c r="F400" s="3" t="s">
+      <c r="F403" s="3" t="s">
         <v>2543</v>
       </c>
-      <c r="G400" s="3" t="s">
+      <c r="G403" s="3" t="s">
         <v>2437</v>
       </c>
-      <c r="H400" s="3" t="s">
+      <c r="H403" s="3" t="s">
         <v>2448</v>
       </c>
-      <c r="I400" s="3" t="s">
+      <c r="I403" s="3" t="s">
         <v>2530</v>
       </c>
-      <c r="J400" s="3" t="s">
+      <c r="J403" s="3" t="s">
         <v>2517</v>
       </c>
-      <c r="K400" s="3" t="s">
+      <c r="K403" s="3" t="s">
         <v>2459</v>
       </c>
-      <c r="L400" s="3" t="s">
+      <c r="L403" s="3" t="s">
         <v>2505</v>
       </c>
-      <c r="M400" s="3" t="s">
+      <c r="M403" s="3" t="s">
         <v>2437</v>
       </c>
-      <c r="N400" s="3" t="s">
+      <c r="N403" s="3" t="s">
         <v>2479</v>
       </c>
-      <c r="O400" s="3" t="s">
+      <c r="O403" s="3" t="s">
         <v>2491</v>
       </c>
-      <c r="P400" s="3" t="s">
+      <c r="P403" s="3" t="s">
         <v>2582</v>
       </c>
     </row>
-    <row r="401" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A401" s="3" t="s">
+    <row r="404" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A404" s="3" t="s">
         <v>3644</v>
       </c>
-      <c r="B401" s="3" t="s">
+      <c r="B404" s="3" t="s">
         <v>2414</v>
       </c>
-      <c r="C401" s="3" t="s">
+      <c r="C404" s="3" t="s">
         <v>2570</v>
       </c>
-      <c r="D401" s="3" t="s">
+      <c r="D404" s="3" t="s">
         <v>2556</v>
       </c>
-      <c r="E401" s="3" t="s">
+      <c r="E404" s="3" t="s">
         <v>1066</v>
       </c>
-      <c r="F401" s="3" t="s">
+      <c r="F404" s="3" t="s">
         <v>2544</v>
       </c>
-      <c r="G401" s="3" t="s">
+      <c r="G404" s="3" t="s">
         <v>1072</v>
       </c>
-      <c r="H401" s="3" t="s">
+      <c r="H404" s="3" t="s">
         <v>1073</v>
       </c>
-      <c r="I401" s="3" t="s">
+      <c r="I404" s="3" t="s">
         <v>2531</v>
       </c>
-      <c r="J401" s="3" t="s">
+      <c r="J404" s="3" t="s">
         <v>2518</v>
       </c>
-      <c r="K401" s="3" t="s">
+      <c r="K404" s="3" t="s">
         <v>2460</v>
       </c>
-      <c r="L401" s="3" t="s">
+      <c r="L404" s="3" t="s">
         <v>1075</v>
       </c>
-      <c r="M401" s="3" t="s">
+      <c r="M404" s="3" t="s">
         <v>1071</v>
       </c>
-      <c r="N401" s="3" t="s">
+      <c r="N404" s="3" t="s">
         <v>1069</v>
       </c>
-      <c r="O401" s="3" t="s">
+      <c r="O404" s="3" t="s">
         <v>2492</v>
       </c>
-      <c r="P401" s="3" t="s">
+      <c r="P404" s="3" t="s">
         <v>2583</v>
       </c>
     </row>
-    <row r="402" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A402" s="3" t="s">
+    <row r="405" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A405" s="3" t="s">
         <v>3640</v>
       </c>
-      <c r="B402" s="3" t="s">
+      <c r="B405" s="3" t="s">
         <v>2412</v>
       </c>
-      <c r="C402" s="3" t="s">
+      <c r="C405" s="3" t="s">
         <v>2571</v>
       </c>
-      <c r="D402" s="3" t="s">
+      <c r="D405" s="3" t="s">
         <v>2557</v>
       </c>
-      <c r="E402" s="3" t="s">
+      <c r="E405" s="3" t="s">
         <v>2412</v>
       </c>
-      <c r="F402" s="3" t="s">
+      <c r="F405" s="3" t="s">
         <v>2545</v>
       </c>
-      <c r="G402" s="3" t="s">
+      <c r="G405" s="3" t="s">
         <v>2438</v>
       </c>
-      <c r="H402" s="3" t="s">
+      <c r="H405" s="3" t="s">
         <v>2449</v>
       </c>
-      <c r="I402" s="3" t="s">
+      <c r="I405" s="3" t="s">
         <v>2532</v>
       </c>
-      <c r="J402" s="3" t="s">
+      <c r="J405" s="3" t="s">
         <v>2519</v>
       </c>
-      <c r="K402" s="3" t="s">
+      <c r="K405" s="3" t="s">
         <v>2412</v>
       </c>
-      <c r="L402" s="3" t="s">
+      <c r="L405" s="3" t="s">
         <v>2506</v>
       </c>
-      <c r="M402" s="3" t="s">
+      <c r="M405" s="3" t="s">
         <v>2438</v>
       </c>
-      <c r="N402" s="3" t="s">
+      <c r="N405" s="3" t="s">
         <v>2480</v>
       </c>
-      <c r="O402" s="3" t="s">
+      <c r="O405" s="3" t="s">
         <v>2503</v>
       </c>
-      <c r="P402" s="3" t="s">
+      <c r="P405" s="3" t="s">
         <v>2584</v>
       </c>
     </row>
-    <row r="403" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A403" s="3" t="s">
+    <row r="406" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A406" s="3" t="s">
         <v>3641</v>
       </c>
-      <c r="B403" s="3" t="s">
+      <c r="B406" s="3" t="s">
         <v>2413</v>
       </c>
-      <c r="C403" s="3" t="s">
+      <c r="C406" s="3" t="s">
         <v>2572</v>
       </c>
-      <c r="D403" s="3" t="s">
+      <c r="D406" s="3" t="s">
         <v>2558</v>
       </c>
-      <c r="E403" s="3" t="s">
+      <c r="E406" s="3" t="s">
         <v>2427</v>
       </c>
-      <c r="F403" s="3" t="s">
+      <c r="F406" s="3" t="s">
         <v>2546</v>
       </c>
-      <c r="G403" s="3" t="s">
+      <c r="G406" s="3" t="s">
         <v>2439</v>
       </c>
-      <c r="H403" s="3" t="s">
+      <c r="H406" s="3" t="s">
         <v>2413</v>
       </c>
-      <c r="I403" s="3" t="s">
+      <c r="I406" s="3" t="s">
         <v>2533</v>
       </c>
-      <c r="J403" s="3" t="s">
+      <c r="J406" s="3" t="s">
         <v>2520</v>
       </c>
-      <c r="K403" s="3" t="s">
+      <c r="K406" s="3" t="s">
         <v>2439</v>
       </c>
-      <c r="L403" s="3" t="s">
+      <c r="L406" s="3" t="s">
         <v>2507</v>
       </c>
-      <c r="M403" s="3" t="s">
+      <c r="M406" s="3" t="s">
         <v>2439</v>
       </c>
-      <c r="N403" s="3" t="s">
+      <c r="N406" s="3" t="s">
         <v>2481</v>
       </c>
-      <c r="O403" s="3" t="s">
+      <c r="O406" s="3" t="s">
         <v>2494</v>
       </c>
-      <c r="P403" s="3" t="s">
+      <c r="P406" s="3" t="s">
         <v>2585</v>
       </c>
     </row>
-    <row r="404" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A404" s="3" t="s">
+    <row r="407" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A407" s="3" t="s">
         <v>3645</v>
       </c>
-      <c r="B404" s="3" t="s">
+      <c r="B407" s="3" t="s">
         <v>2416</v>
       </c>
-      <c r="C404" s="3" t="s">
+      <c r="C407" s="3" t="s">
         <v>2573</v>
       </c>
-      <c r="D404" s="3" t="s">
+      <c r="D407" s="3" t="s">
         <v>2559</v>
       </c>
-      <c r="E404" s="3" t="s">
+      <c r="E407" s="3" t="s">
         <v>2428</v>
       </c>
-      <c r="F404" s="3" t="s">
+      <c r="F407" s="3" t="s">
         <v>2547</v>
       </c>
-      <c r="G404" s="3" t="s">
+      <c r="G407" s="3" t="s">
         <v>2440</v>
       </c>
-      <c r="H404" s="3" t="s">
+      <c r="H407" s="3" t="s">
         <v>2450</v>
       </c>
-      <c r="I404" s="3" t="s">
+      <c r="I407" s="3" t="s">
         <v>2534</v>
       </c>
-      <c r="J404" s="3" t="s">
+      <c r="J407" s="3" t="s">
         <v>2521</v>
       </c>
-      <c r="K404" s="3" t="s">
+      <c r="K407" s="3" t="s">
         <v>2461</v>
       </c>
-      <c r="L404" s="3" t="s">
+      <c r="L407" s="3" t="s">
         <v>2508</v>
       </c>
-      <c r="M404" s="3" t="s">
+      <c r="M407" s="3" t="s">
         <v>2469</v>
       </c>
-      <c r="N404" s="3" t="s">
+      <c r="N407" s="3" t="s">
         <v>2482</v>
       </c>
-      <c r="O404" s="3" t="s">
+      <c r="O407" s="3" t="s">
         <v>2493</v>
       </c>
-      <c r="P404" s="3" t="s">
+      <c r="P407" s="3" t="s">
         <v>2586</v>
       </c>
     </row>
-    <row r="405" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A405" s="3" t="s">
+    <row r="408" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A408" s="3" t="s">
         <v>3646</v>
       </c>
-      <c r="B405" s="3" t="s">
+      <c r="B408" s="3" t="s">
         <v>2417</v>
       </c>
-      <c r="C405" s="3" t="s">
+      <c r="C408" s="3" t="s">
         <v>2574</v>
       </c>
-      <c r="D405" s="3" t="s">
+      <c r="D408" s="3" t="s">
         <v>2560</v>
       </c>
-      <c r="E405" s="3" t="s">
+      <c r="E408" s="3" t="s">
         <v>2429</v>
       </c>
-      <c r="F405" s="3" t="s">
+      <c r="F408" s="3" t="s">
         <v>2548</v>
       </c>
-      <c r="G405" s="3" t="s">
+      <c r="G408" s="3" t="s">
         <v>2441</v>
       </c>
-      <c r="H405" s="3" t="s">
+      <c r="H408" s="3" t="s">
         <v>2451</v>
       </c>
-      <c r="I405" s="3" t="s">
+      <c r="I408" s="3" t="s">
         <v>2535</v>
       </c>
-      <c r="J405" s="3" t="s">
+      <c r="J408" s="3" t="s">
         <v>2522</v>
       </c>
-      <c r="K405" s="3" t="s">
+      <c r="K408" s="3" t="s">
         <v>2462</v>
       </c>
-      <c r="L405" s="3" t="s">
+      <c r="L408" s="3" t="s">
         <v>2509</v>
       </c>
-      <c r="M405" s="3" t="s">
+      <c r="M408" s="3" t="s">
         <v>2470</v>
       </c>
-      <c r="N405" s="3" t="s">
+      <c r="N408" s="3" t="s">
         <v>2483</v>
       </c>
-      <c r="O405" s="3" t="s">
+      <c r="O408" s="3" t="s">
         <v>2500</v>
       </c>
-      <c r="P405" s="3" t="s">
+      <c r="P408" s="3" t="s">
         <v>2587</v>
       </c>
     </row>
-    <row r="406" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A406" s="3" t="s">
+    <row r="409" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A409" s="3" t="s">
         <v>3647</v>
       </c>
-      <c r="B406" s="3" t="s">
+      <c r="B409" s="3" t="s">
         <v>2418</v>
       </c>
-      <c r="C406" s="3" t="s">
+      <c r="C409" s="3" t="s">
         <v>2575</v>
       </c>
-      <c r="D406" s="3" t="s">
+      <c r="D409" s="3" t="s">
         <v>2561</v>
       </c>
-      <c r="E406" s="3" t="s">
+      <c r="E409" s="3" t="s">
         <v>2430</v>
       </c>
-      <c r="F406" s="3" t="s">
+      <c r="F409" s="3" t="s">
         <v>2549</v>
       </c>
-      <c r="G406" s="3" t="s">
+      <c r="G409" s="3" t="s">
         <v>2502</v>
       </c>
-      <c r="H406" s="3" t="s">
+      <c r="H409" s="3" t="s">
         <v>2452</v>
       </c>
-      <c r="I406" s="3" t="s">
+      <c r="I409" s="3" t="s">
         <v>2536</v>
       </c>
-      <c r="J406" s="3" t="s">
+      <c r="J409" s="3" t="s">
         <v>2523</v>
       </c>
-      <c r="K406" s="3" t="s">
+      <c r="K409" s="3" t="s">
         <v>2463</v>
       </c>
-      <c r="L406" s="3" t="s">
+      <c r="L409" s="3" t="s">
         <v>2510</v>
       </c>
-      <c r="M406" s="3" t="s">
+      <c r="M409" s="3" t="s">
         <v>2471</v>
       </c>
-      <c r="N406" s="3" t="s">
+      <c r="N409" s="3" t="s">
         <v>2484</v>
       </c>
-      <c r="O406" s="3" t="s">
+      <c r="O409" s="3" t="s">
         <v>2501</v>
       </c>
-      <c r="P406" s="3" t="s">
+      <c r="P409" s="3" t="s">
         <v>2588</v>
       </c>
     </row>
-    <row r="407" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A407" s="3" t="s">
+    <row r="410" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A410" s="3" t="s">
         <v>3648</v>
       </c>
-      <c r="B407" s="3" t="s">
+      <c r="B410" s="3" t="s">
         <v>2419</v>
       </c>
-      <c r="C407" s="3" t="s">
+      <c r="C410" s="3" t="s">
         <v>2576</v>
       </c>
-      <c r="D407" s="3" t="s">
+      <c r="D410" s="3" t="s">
         <v>2562</v>
       </c>
-      <c r="E407" s="3" t="s">
+      <c r="E410" s="3" t="s">
         <v>2431</v>
       </c>
-      <c r="F407" s="3" t="s">
+      <c r="F410" s="3" t="s">
         <v>2550</v>
       </c>
-      <c r="G407" s="3" t="s">
+      <c r="G410" s="3" t="s">
         <v>2442</v>
       </c>
-      <c r="H407" s="3" t="s">
+      <c r="H410" s="3" t="s">
         <v>2457</v>
       </c>
-      <c r="I407" s="3" t="s">
+      <c r="I410" s="3" t="s">
         <v>2537</v>
       </c>
-      <c r="J407" s="3" t="s">
+      <c r="J410" s="3" t="s">
         <v>2524</v>
       </c>
-      <c r="K407" s="3" t="s">
+      <c r="K410" s="3" t="s">
         <v>2468</v>
       </c>
-      <c r="L407" s="3" t="s">
+      <c r="L410" s="3" t="s">
         <v>2511</v>
       </c>
-      <c r="M407" s="3" t="s">
+      <c r="M410" s="3" t="s">
         <v>2472</v>
       </c>
-      <c r="N407" s="3" t="s">
+      <c r="N410" s="3" t="s">
         <v>2485</v>
       </c>
-      <c r="O407" s="3" t="s">
+      <c r="O410" s="3" t="s">
         <v>2495</v>
       </c>
-      <c r="P407" s="3" t="s">
+      <c r="P410" s="3" t="s">
         <v>2589</v>
       </c>
     </row>
-    <row r="408" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A408" s="3" t="s">
+    <row r="411" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A411" s="3" t="s">
         <v>3649</v>
       </c>
-      <c r="B408" s="3" t="s">
+      <c r="B411" s="3" t="s">
         <v>2420</v>
       </c>
-      <c r="C408" s="3" t="s">
+      <c r="C411" s="3" t="s">
         <v>2577</v>
       </c>
-      <c r="D408" s="3" t="s">
+      <c r="D411" s="3" t="s">
         <v>2563</v>
       </c>
-      <c r="E408" s="3" t="s">
+      <c r="E411" s="3" t="s">
         <v>2435</v>
       </c>
-      <c r="F408" s="3" t="s">
+      <c r="F411" s="3" t="s">
         <v>2551</v>
       </c>
-      <c r="G408" s="3" t="s">
+      <c r="G411" s="3" t="s">
         <v>2443</v>
       </c>
-      <c r="H408" s="3" t="s">
+      <c r="H411" s="3" t="s">
         <v>2456</v>
       </c>
-      <c r="I408" s="3" t="s">
+      <c r="I411" s="3" t="s">
         <v>2538</v>
       </c>
-      <c r="J408" s="3" t="s">
+      <c r="J411" s="3" t="s">
         <v>2525</v>
       </c>
-      <c r="K408" s="3" t="s">
+      <c r="K411" s="3" t="s">
         <v>2467</v>
       </c>
-      <c r="L408" s="3" t="s">
+      <c r="L411" s="3" t="s">
         <v>2512</v>
       </c>
-      <c r="M408" s="3" t="s">
+      <c r="M411" s="3" t="s">
         <v>2473</v>
       </c>
-      <c r="N408" s="3" t="s">
+      <c r="N411" s="3" t="s">
         <v>2486</v>
       </c>
-      <c r="O408" s="3" t="s">
+      <c r="O411" s="3" t="s">
         <v>2496</v>
       </c>
-      <c r="P408" s="3" t="s">
+      <c r="P411" s="3" t="s">
         <v>2590</v>
       </c>
     </row>
-    <row r="409" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A409" s="3" t="s">
+    <row r="412" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A412" s="3" t="s">
         <v>3650</v>
       </c>
-      <c r="B409" s="3" t="s">
+      <c r="B412" s="3" t="s">
         <v>2423</v>
       </c>
-      <c r="C409" s="3" t="s">
+      <c r="C412" s="3" t="s">
         <v>2579</v>
       </c>
-      <c r="D409" s="3" t="s">
+      <c r="D412" s="3" t="s">
         <v>2565</v>
       </c>
-      <c r="E409" s="3" t="s">
+      <c r="E412" s="3" t="s">
         <v>2433</v>
       </c>
-      <c r="F409" s="3" t="s">
+      <c r="F412" s="3" t="s">
         <v>2553</v>
       </c>
-      <c r="G409" s="3" t="s">
+      <c r="G412" s="3" t="s">
         <v>2446</v>
       </c>
-      <c r="H409" s="3" t="s">
+      <c r="H412" s="3" t="s">
         <v>2455</v>
       </c>
-      <c r="I409" s="3" t="s">
+      <c r="I412" s="3" t="s">
         <v>2540</v>
       </c>
-      <c r="J409" s="3" t="s">
+      <c r="J412" s="3" t="s">
         <v>2527</v>
       </c>
-      <c r="K409" s="3" t="s">
+      <c r="K412" s="3" t="s">
         <v>2466</v>
       </c>
-      <c r="L409" s="3" t="s">
+      <c r="L412" s="3" t="s">
         <v>2514</v>
       </c>
-      <c r="M409" s="3" t="s">
+      <c r="M412" s="3" t="s">
         <v>2475</v>
       </c>
-      <c r="N409" s="3" t="s">
+      <c r="N412" s="3" t="s">
         <v>2488</v>
       </c>
-      <c r="O409" s="3" t="s">
+      <c r="O412" s="3" t="s">
         <v>2499</v>
       </c>
-      <c r="P409" s="3" t="s">
+      <c r="P412" s="3" t="s">
         <v>2592</v>
       </c>
     </row>
-    <row r="411" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A411" s="3" t="s">
+    <row r="414" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A414" s="3" t="s">
         <v>3331</v>
       </c>
-      <c r="B411" s="3" t="s">
+      <c r="B414" s="3" t="s">
         <v>3332</v>
       </c>
-      <c r="C411" s="3" t="s">
+      <c r="C414" s="3" t="s">
         <v>3337</v>
       </c>
-      <c r="D411" s="3" t="s">
+      <c r="D414" s="3" t="s">
         <v>3338</v>
       </c>
-      <c r="E411" s="3" t="s">
+      <c r="E414" s="3" t="s">
         <v>3340</v>
       </c>
-      <c r="F411" s="3" t="s">
+      <c r="F414" s="3" t="s">
         <v>3341</v>
       </c>
-      <c r="G411" s="3" t="s">
+      <c r="G414" s="3" t="s">
         <v>3342</v>
       </c>
-      <c r="H411" s="3" t="s">
+      <c r="H414" s="3" t="s">
         <v>3343</v>
       </c>
-      <c r="I411" s="3" t="s">
+      <c r="I414" s="3" t="s">
         <v>3335</v>
       </c>
-      <c r="J411" s="3" t="s">
+      <c r="J414" s="3" t="s">
         <v>3336</v>
       </c>
-      <c r="K411" s="3" t="s">
+      <c r="K414" s="3" t="s">
         <v>3344</v>
       </c>
-      <c r="L411" s="3" t="s">
+      <c r="L414" s="3" t="s">
         <v>3345</v>
       </c>
-      <c r="M411" s="3" t="s">
+      <c r="M414" s="3" t="s">
         <v>3346</v>
       </c>
-      <c r="N411" s="3" t="s">
+      <c r="N414" s="3" t="s">
         <v>3347</v>
       </c>
-      <c r="O411" s="3" t="s">
+      <c r="O414" s="3" t="s">
         <v>3348</v>
       </c>
-      <c r="P411" s="3" t="s">
+      <c r="P414" s="3" t="s">
         <v>3339</v>
       </c>
     </row>
-    <row r="412" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A412" s="3" t="s">
+    <row r="415" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A415" s="3" t="s">
         <v>3653</v>
       </c>
-      <c r="B412" s="3" t="s">
+      <c r="B415" s="3" t="s">
         <v>3732</v>
       </c>
-      <c r="C412" s="3" t="s">
+      <c r="C415" s="3" t="s">
         <v>3733</v>
       </c>
-      <c r="D412" s="3" t="s">
+      <c r="D415" s="3" t="s">
         <v>3734</v>
       </c>
-      <c r="E412" s="3" t="s">
+      <c r="E415" s="3" t="s">
         <v>3735</v>
       </c>
-      <c r="F412" s="3" t="s">
+      <c r="F415" s="3" t="s">
         <v>3736</v>
       </c>
-      <c r="G412" s="3" t="s">
+      <c r="G415" s="3" t="s">
         <v>3737</v>
       </c>
-      <c r="H412" s="3" t="s">
+      <c r="H415" s="3" t="s">
         <v>3738</v>
       </c>
-      <c r="I412" s="3" t="s">
+      <c r="I415" s="3" t="s">
         <v>3739</v>
       </c>
-      <c r="J412" s="3" t="s">
+      <c r="J415" s="3" t="s">
         <v>3740</v>
       </c>
-      <c r="K412" s="3" t="s">
+      <c r="K415" s="3" t="s">
         <v>3741</v>
       </c>
-      <c r="L412" s="3" t="s">
+      <c r="L415" s="3" t="s">
         <v>3731</v>
       </c>
-      <c r="M412" s="3" t="s">
+      <c r="M415" s="3" t="s">
         <v>3742</v>
       </c>
-      <c r="N412" s="3" t="s">
+      <c r="N415" s="3" t="s">
         <v>3730</v>
       </c>
-      <c r="O412" s="3" t="s">
+      <c r="O415" s="3" t="s">
         <v>3728</v>
       </c>
-      <c r="P412" s="3" t="s">
+      <c r="P415" s="3" t="s">
         <v>3729</v>
       </c>
     </row>
-    <row r="413" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A413" s="3" t="s">
+    <row r="416" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A416" s="3" t="s">
         <v>3321</v>
       </c>
-      <c r="B413" s="3" t="s">
+      <c r="B416" s="3" t="s">
         <v>3322</v>
       </c>
-      <c r="C413" s="3" t="s">
+      <c r="C416" s="3" t="s">
         <v>3360</v>
       </c>
-      <c r="D413" s="3" t="s">
+      <c r="D416" s="3" t="s">
         <v>3361</v>
       </c>
-      <c r="E413" s="3" t="s">
+      <c r="E416" s="3" t="s">
         <v>3357</v>
       </c>
-      <c r="F413" s="3" t="s">
+      <c r="F416" s="3" t="s">
         <v>3358</v>
       </c>
-      <c r="G413" s="3" t="s">
+      <c r="G416" s="3" t="s">
         <v>3351</v>
       </c>
-      <c r="H413" s="3" t="s">
+      <c r="H416" s="3" t="s">
         <v>3352</v>
       </c>
-      <c r="I413" s="3" t="s">
+      <c r="I416" s="3" t="s">
         <v>3359</v>
       </c>
-      <c r="J413" s="3" t="s">
+      <c r="J416" s="3" t="s">
         <v>3356</v>
       </c>
-      <c r="K413" s="3" t="s">
+      <c r="K416" s="3" t="s">
         <v>3353</v>
       </c>
-      <c r="L413" s="3" t="s">
+      <c r="L416" s="3" t="s">
         <v>3355</v>
       </c>
-      <c r="M413" s="3" t="s">
+      <c r="M416" s="3" t="s">
         <v>3354</v>
       </c>
-      <c r="N413" s="3" t="s">
+      <c r="N416" s="3" t="s">
         <v>3350</v>
       </c>
-      <c r="O413" s="3" t="s">
+      <c r="O416" s="3" t="s">
         <v>3349</v>
       </c>
-      <c r="P413" s="3" t="s">
+      <c r="P416" s="3" t="s">
         <v>3362</v>
       </c>
     </row>
-    <row r="414" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A414" s="3" t="s">
+    <row r="417" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A417" s="3" t="s">
         <v>3323</v>
       </c>
-      <c r="B414" s="3" t="s">
+      <c r="B417" s="3" t="s">
         <v>3327</v>
       </c>
-      <c r="C414" s="3" t="s">
+      <c r="C417" s="3" t="s">
         <v>3365</v>
       </c>
-      <c r="D414" s="3" t="s">
+      <c r="D417" s="3" t="s">
         <v>3364</v>
       </c>
-      <c r="E414" s="3" t="s">
+      <c r="E417" s="3" t="s">
         <v>3366</v>
       </c>
-      <c r="F414" s="3" t="s">
+      <c r="F417" s="3" t="s">
         <v>3367</v>
       </c>
-      <c r="G414" s="3" t="s">
+      <c r="G417" s="3" t="s">
         <v>3368</v>
       </c>
-      <c r="H414" s="3" t="s">
+      <c r="H417" s="3" t="s">
         <v>3369</v>
       </c>
-      <c r="I414" s="3" t="s">
+      <c r="I417" s="3" t="s">
         <v>3370</v>
       </c>
-      <c r="J414" s="3" t="s">
+      <c r="J417" s="3" t="s">
         <v>3371</v>
       </c>
-      <c r="K414" s="3" t="s">
+      <c r="K417" s="3" t="s">
         <v>3372</v>
       </c>
-      <c r="L414" s="3" t="s">
+      <c r="L417" s="3" t="s">
         <v>3373</v>
       </c>
-      <c r="M414" s="3" t="s">
+      <c r="M417" s="3" t="s">
         <v>3374</v>
       </c>
-      <c r="N414" s="3" t="s">
+      <c r="N417" s="3" t="s">
         <v>3375</v>
       </c>
-      <c r="O414" s="3" t="s">
+      <c r="O417" s="3" t="s">
         <v>3376</v>
       </c>
-      <c r="P414" s="3" t="s">
+      <c r="P417" s="3" t="s">
         <v>3363</v>
       </c>
     </row>
-    <row r="415" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A415" s="3" t="s">
+    <row r="418" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A418" s="3" t="s">
         <v>3324</v>
       </c>
-      <c r="B415" s="3" t="s">
+      <c r="B418" s="3" t="s">
         <v>3328</v>
       </c>
-      <c r="C415" s="3" t="s">
+      <c r="C418" s="3" t="s">
         <v>3379</v>
       </c>
-      <c r="D415" s="3" t="s">
+      <c r="D418" s="3" t="s">
         <v>3380</v>
       </c>
-      <c r="E415" s="3" t="s">
+      <c r="E418" s="3" t="s">
         <v>3382</v>
       </c>
-      <c r="F415" s="3" t="s">
+      <c r="F418" s="3" t="s">
         <v>3383</v>
       </c>
-      <c r="G415" s="3" t="s">
+      <c r="G418" s="3" t="s">
         <v>3384</v>
       </c>
-      <c r="H415" s="3" t="s">
+      <c r="H418" s="3" t="s">
         <v>3385</v>
       </c>
-      <c r="I415" s="3" t="s">
+      <c r="I418" s="3" t="s">
         <v>3386</v>
       </c>
-      <c r="J415" s="3" t="s">
+      <c r="J418" s="3" t="s">
         <v>3387</v>
       </c>
-      <c r="K415" s="3" t="s">
+      <c r="K418" s="3" t="s">
         <v>3388</v>
       </c>
-      <c r="L415" s="3" t="s">
+      <c r="L418" s="3" t="s">
         <v>3389</v>
       </c>
-      <c r="M415" s="3" t="s">
+      <c r="M418" s="3" t="s">
         <v>3390</v>
       </c>
-      <c r="N415" s="3" t="s">
+      <c r="N418" s="3" t="s">
         <v>3378</v>
       </c>
-      <c r="O415" s="3" t="s">
+      <c r="O418" s="3" t="s">
         <v>3377</v>
       </c>
-      <c r="P415" s="3" t="s">
+      <c r="P418" s="3" t="s">
         <v>3381</v>
       </c>
     </row>
-    <row r="416" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A416" s="3" t="s">
+    <row r="419" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A419" s="3" t="s">
         <v>3325</v>
       </c>
-      <c r="B416" s="3" t="s">
+      <c r="B419" s="3" t="s">
         <v>3329</v>
       </c>
-      <c r="C416" s="3" t="s">
+      <c r="C419" s="3" t="s">
         <v>3396</v>
       </c>
-      <c r="D416" s="3" t="s">
+      <c r="D419" s="3" t="s">
         <v>3397</v>
       </c>
-      <c r="E416" s="3" t="s">
+      <c r="E419" s="3" t="s">
         <v>3399</v>
       </c>
-      <c r="F416" s="3" t="s">
+      <c r="F419" s="3" t="s">
         <v>3400</v>
       </c>
-      <c r="G416" s="3" t="s">
+      <c r="G419" s="3" t="s">
         <v>3401</v>
       </c>
-      <c r="H416" s="3" t="s">
+      <c r="H419" s="3" t="s">
         <v>3402</v>
       </c>
-      <c r="I416" s="3" t="s">
+      <c r="I419" s="3" t="s">
         <v>3403</v>
       </c>
-      <c r="J416" s="3" t="s">
+      <c r="J419" s="3" t="s">
         <v>3404</v>
       </c>
-      <c r="K416" s="3" t="s">
+      <c r="K419" s="3" t="s">
         <v>3392</v>
       </c>
-      <c r="L416" s="3" t="s">
+      <c r="L419" s="3" t="s">
         <v>3393</v>
       </c>
-      <c r="M416" s="3" t="s">
+      <c r="M419" s="3" t="s">
         <v>3391</v>
       </c>
-      <c r="N416" s="3" t="s">
+      <c r="N419" s="3" t="s">
         <v>3394</v>
       </c>
-      <c r="O416" s="3" t="s">
+      <c r="O419" s="3" t="s">
         <v>3395</v>
       </c>
-      <c r="P416" s="3" t="s">
+      <c r="P419" s="3" t="s">
         <v>3398</v>
       </c>
     </row>
-    <row r="417" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A417" s="3" t="s">
+    <row r="420" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A420" s="3" t="s">
         <v>3326</v>
       </c>
-      <c r="B417" s="3" t="s">
+      <c r="B420" s="3" t="s">
         <v>3330</v>
       </c>
-      <c r="C417" s="3" t="s">
+      <c r="C420" s="3" t="s">
         <v>3413</v>
       </c>
-      <c r="D417" s="3" t="s">
+      <c r="D420" s="3" t="s">
         <v>3412</v>
       </c>
-      <c r="E417" s="3" t="s">
+      <c r="E420" s="3" t="s">
         <v>3415</v>
       </c>
-      <c r="F417" s="3" t="s">
+      <c r="F420" s="3" t="s">
         <v>3416</v>
       </c>
-      <c r="G417" s="3" t="s">
+      <c r="G420" s="3" t="s">
         <v>3417</v>
       </c>
-      <c r="H417" s="3" t="s">
+      <c r="H420" s="3" t="s">
         <v>3418</v>
       </c>
-      <c r="I417" s="3" t="s">
+      <c r="I420" s="3" t="s">
         <v>3406</v>
       </c>
-      <c r="J417" s="3" t="s">
+      <c r="J420" s="3" t="s">
         <v>3405</v>
       </c>
-      <c r="K417" s="3" t="s">
+      <c r="K420" s="3" t="s">
         <v>3407</v>
       </c>
-      <c r="L417" s="3" t="s">
+      <c r="L420" s="3" t="s">
         <v>3408</v>
       </c>
-      <c r="M417" s="3" t="s">
+      <c r="M420" s="3" t="s">
         <v>3409</v>
       </c>
-      <c r="N417" s="3" t="s">
+      <c r="N420" s="3" t="s">
         <v>3410</v>
       </c>
-      <c r="O417" s="3" t="s">
+      <c r="O420" s="3" t="s">
         <v>3411</v>
       </c>
-      <c r="P417" s="3" t="s">
+      <c r="P420" s="3" t="s">
         <v>3414</v>
       </c>
     </row>
-    <row r="418" spans="1:16" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A418" s="3" t="s">
+    <row r="421" spans="1:16" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A421" s="3" t="s">
         <v>3333</v>
       </c>
-      <c r="B418" s="3" t="s">
+      <c r="B421" s="3" t="s">
         <v>3334</v>
       </c>
-      <c r="C418" s="3" t="s">
+      <c r="C421" s="3" t="s">
         <v>3428</v>
       </c>
-      <c r="D418" s="3" t="s">
+      <c r="D421" s="3" t="s">
         <v>3429</v>
       </c>
-      <c r="E418" s="3" t="s">
+      <c r="E421" s="3" t="s">
         <v>3431</v>
       </c>
-      <c r="F418" s="3" t="s">
+      <c r="F421" s="3" t="s">
         <v>3432</v>
       </c>
-      <c r="G418" s="3" t="s">
+      <c r="G421" s="3" t="s">
         <v>3420</v>
       </c>
-      <c r="H418" s="3" t="s">
+      <c r="H421" s="3" t="s">
         <v>3419</v>
       </c>
-      <c r="I418" s="3" t="s">
+      <c r="I421" s="3" t="s">
         <v>3421</v>
       </c>
-      <c r="J418" s="3" t="s">
+      <c r="J421" s="3" t="s">
         <v>3422</v>
       </c>
-      <c r="K418" s="3" t="s">
+      <c r="K421" s="3" t="s">
         <v>3424</v>
       </c>
-      <c r="L418" s="3" t="s">
+      <c r="L421" s="3" t="s">
         <v>3425</v>
       </c>
-      <c r="M418" s="4" t="s">
+      <c r="M421" s="4" t="s">
         <v>3423</v>
       </c>
-      <c r="N418" s="3" t="s">
+      <c r="N421" s="3" t="s">
         <v>3426</v>
       </c>
-      <c r="O418" s="3" t="s">
+      <c r="O421" s="3" t="s">
         <v>3427</v>
       </c>
-      <c r="P418" s="3" t="s">
+      <c r="P421" s="3" t="s">
         <v>3430</v>
       </c>
     </row>
